--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="171">
   <si>
     <t>To. 개발 : 스크립트 수정 시, 파란색으로 칠해둘 것!!</t>
   </si>
@@ -9421,7 +9421,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna_Fall_Start")</f>
         <v>Anna_Fall_Start</v>
       </c>
-      <c r="D18" s="29"/>
+      <c r="D18" s="29" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
+        <v>Right</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -11290,6 +11293,9 @@
       <c r="M65" s="62" t="s">
         <v>165</v>
       </c>
+      <c r="N65" s="7" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="68">

--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="251">
   <si>
     <t>To. 개발 : 스크립트 수정 시, 파란색으로 칠해둘 것!!</t>
   </si>
@@ -290,6 +290,15 @@
   </si>
   <si>
     <t>뭐라도 하겠지</t>
+  </si>
+  <si>
+    <t>0으로 해두면 동시에 됨 / 0.5 = 앞에 거 0.5초 뒤에 다음 거 재생</t>
+  </si>
+  <si>
+    <t>무한정으로 하면 부하가 생김 이 정도까지만 최대 병렬만 하겠다하는 숫자를 알려주면 그 숫자 내에서 병렬 처리를 함</t>
+  </si>
+  <si>
+    <t>선택지, 스크립트, 이벤트(클릭 등) 이 3개는 직렬로만 선택이 됨</t>
   </si>
   <si>
     <t>비고</t>
@@ -1345,7 +1354,7 @@
     <xdr:ext cx="3524250" cy="695325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1373,7 +1382,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2017,6 +2026,21 @@
       <c r="F25" s="30"/>
       <c r="G25" s="30"/>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="E11:G11"/>
@@ -2058,7 +2082,7 @@
         <v>NextID</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -2117,7 +2141,7 @@
         <v>101004</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -2138,7 +2162,7 @@
         <v>101005</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -2197,7 +2221,7 @@
         <v>101008</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -2218,7 +2242,7 @@
         <v>101009</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -2239,7 +2263,7 @@
         <v>101010</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -2260,7 +2284,7 @@
         <v>101011</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -2281,7 +2305,7 @@
         <v>101012</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
@@ -2302,7 +2326,7 @@
         <v>101013</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -2323,7 +2347,7 @@
         <v>101014</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -2344,7 +2368,7 @@
         <v>101015</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -2365,7 +2389,7 @@
         <v>101016</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
@@ -2386,7 +2410,7 @@
         <v>101017</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -2407,7 +2431,7 @@
         <v>101018</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -2447,7 +2471,7 @@
         <v>101020</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
@@ -2540,7 +2564,7 @@
         <v>101025</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
@@ -9730,7 +9754,7 @@
         <v>Script</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2">
@@ -10582,7 +10606,7 @@
         <v>Duration</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -10642,7 +10666,7 @@
         <v>-1</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -11066,8 +11090,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
         <v>104011</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
+      <c r="B28" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
+        <v>Anna</v>
+      </c>
+      <c r="C28" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
+        <v>CameraShift</v>
+      </c>
       <c r="D28" s="34"/>
       <c r="E28" s="34"/>
     </row>
@@ -11967,7 +11997,7 @@
         <v>Name</v>
       </c>
       <c r="D1" s="48" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY('통합'!A:AA, ""SELECT R WHERE D CONTAINS 'Select'"")"),"ChoiceCount")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY('통합'!A:AA, ""SELECT R WHERE C CONTAINS 'Select'"")"),"ChoiceCount")</f>
         <v>ChoiceCount</v>
       </c>
     </row>
@@ -11984,8 +12014,9 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
         <v>Anna</v>
       </c>
-      <c r="D2" s="4">
-        <v>2.0</v>
+      <c r="D2" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -12001,6 +12032,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Obstacle_H")</f>
         <v>Obstacle_H</v>
       </c>
+      <c r="D3" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="34">
@@ -12012,6 +12047,7 @@
         <v>무엇을 물을까?</v>
       </c>
       <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -12058,7 +12094,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="61.25"/>
-    <col customWidth="1" min="3" max="3" width="15.25"/>
+    <col customWidth="1" min="3" max="3" width="23.13"/>
     <col customWidth="1" min="6" max="6" width="13.13"/>
     <col customWidth="1" min="7" max="7" width="16.25"/>
     <col customWidth="1" min="8" max="8" width="10.75"/>
@@ -12073,52 +12109,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="50" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B1" s="50" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E1" s="51" t="s">
         <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H1" s="39" t="s">
         <v>62</v>
       </c>
       <c r="I1" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="39" t="s">
         <v>90</v>
-      </c>
-      <c r="J1" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="K1" s="39" t="s">
-        <v>87</v>
       </c>
       <c r="L1" s="44" t="s">
         <v>62</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O1" s="46" t="s">
         <v>62</v>
       </c>
       <c r="P1" s="46" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q1" s="52" t="s">
         <v>62</v>
@@ -12127,7 +12163,7 @@
         <v>63</v>
       </c>
       <c r="S1" s="53" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
@@ -12148,10 +12184,10 @@
         <v>21</v>
       </c>
       <c r="M2" s="55" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N2" s="55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
@@ -12172,10 +12208,10 @@
         <v>21</v>
       </c>
       <c r="M3" s="55" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="N3" s="55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
@@ -12183,7 +12219,7 @@
         <v>101003.0</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>52</v>
@@ -12195,10 +12231,10 @@
         <v>101004.0</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
@@ -12206,7 +12242,7 @@
         <v>101004.0</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>52</v>
@@ -12218,10 +12254,10 @@
         <v>101005.0</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
@@ -12242,10 +12278,10 @@
         <v>21</v>
       </c>
       <c r="M6" s="55" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N6" s="55" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -12266,10 +12302,10 @@
         <v>21</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N7" s="55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -12277,7 +12313,7 @@
         <v>101007.0</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -12289,10 +12325,10 @@
         <v>101008.0</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -12300,7 +12336,7 @@
         <v>101008.0</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>52</v>
@@ -12312,10 +12348,10 @@
         <v>101009.0</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -12323,10 +12359,10 @@
         <v>101009.0</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D10" s="6">
         <v>0.0</v>
@@ -12338,7 +12374,7 @@
       <c r="G10" s="57"/>
       <c r="H10" s="60"/>
       <c r="I10" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J10" s="60">
         <v>7.0</v>
@@ -12350,7 +12386,7 @@
         <v>21</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q10" s="37"/>
       <c r="R10" s="37"/>
@@ -12360,10 +12396,10 @@
         <v>101010.0</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D11" s="6">
         <v>0.0</v>
@@ -12375,7 +12411,7 @@
       <c r="G11" s="57"/>
       <c r="H11" s="60"/>
       <c r="I11" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J11" s="60">
         <v>6.0</v>
@@ -12387,7 +12423,7 @@
         <v>21</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q11" s="37"/>
       <c r="R11" s="37"/>
@@ -12397,10 +12433,10 @@
         <v>101011.0</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D12" s="6">
         <v>2.0</v>
@@ -12412,7 +12448,7 @@
       <c r="G12" s="57"/>
       <c r="H12" s="60"/>
       <c r="I12" s="61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J12" s="60">
         <v>0.05</v>
@@ -12424,7 +12460,7 @@
         <v>21</v>
       </c>
       <c r="P12" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q12" s="37"/>
       <c r="R12" s="37"/>
@@ -12434,7 +12470,7 @@
         <v>101012.0</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>32</v>
@@ -12448,10 +12484,10 @@
       <c r="F13" s="6"/>
       <c r="G13" s="57"/>
       <c r="H13" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J13" s="60"/>
       <c r="K13" s="60"/>
@@ -12465,7 +12501,7 @@
         <v>101013.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>40</v>
@@ -12490,10 +12526,10 @@
         <v>101014.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D15" s="6">
         <v>0.0</v>
@@ -12507,7 +12543,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="63" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J15" s="60"/>
       <c r="K15" s="60"/>
@@ -12515,7 +12551,7 @@
         <v>21</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q15" s="37"/>
       <c r="R15" s="37"/>
@@ -12525,7 +12561,7 @@
         <v>101015.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>55</v>
@@ -12546,7 +12582,7 @@
         <v>21</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q16" s="37"/>
       <c r="R16" s="37"/>
@@ -12556,7 +12592,7 @@
         <v>101016.0</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>32</v>
@@ -12571,7 +12607,7 @@
       <c r="G17" s="57"/>
       <c r="H17" s="60"/>
       <c r="I17" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J17" s="60">
         <v>5.5</v>
@@ -12589,7 +12625,7 @@
         <v>101017.0</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>32</v>
@@ -12604,7 +12640,7 @@
       <c r="G18" s="57"/>
       <c r="H18" s="60"/>
       <c r="I18" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J18" s="60">
         <v>5.0</v>
@@ -12622,10 +12658,10 @@
         <v>101018.0</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" s="65">
         <v>0.0</v>
@@ -12640,13 +12676,13 @@
       <c r="J19" s="62"/>
       <c r="K19" s="62"/>
       <c r="L19" s="34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N19" s="34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O19" s="67"/>
       <c r="P19" s="68"/>
@@ -12658,10 +12694,10 @@
         <v>101019.0</v>
       </c>
       <c r="B20" s="59" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D20" s="65">
         <v>0.0</v>
@@ -12675,7 +12711,7 @@
         <v>21</v>
       </c>
       <c r="I20" s="63" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J20" s="62"/>
       <c r="K20" s="62"/>
@@ -12683,7 +12719,7 @@
         <v>21</v>
       </c>
       <c r="P20" s="68" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q20" s="68"/>
       <c r="R20" s="68"/>
@@ -12693,7 +12729,7 @@
         <v>101020.0</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C21" s="64" t="s">
         <v>24</v>
@@ -12711,13 +12747,13 @@
       <c r="J21" s="62"/>
       <c r="K21" s="62"/>
       <c r="L21" s="34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N21" s="34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O21" s="67"/>
       <c r="P21" s="68"/>
@@ -12729,7 +12765,7 @@
         <v>101021.0</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C22" s="64" t="s">
         <v>40</v>
@@ -12756,7 +12792,7 @@
         <v>101022.0</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C23" s="64" t="s">
         <v>24</v>
@@ -12774,13 +12810,13 @@
       <c r="J23" s="62"/>
       <c r="K23" s="62"/>
       <c r="L23" s="34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O23" s="67"/>
       <c r="P23" s="68"/>
@@ -12792,7 +12828,7 @@
         <v>101023.0</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C24" s="64" t="s">
         <v>24</v>
@@ -12810,13 +12846,13 @@
       <c r="J24" s="62"/>
       <c r="K24" s="62"/>
       <c r="L24" s="34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O24" s="67"/>
       <c r="P24" s="68"/>
@@ -12828,7 +12864,7 @@
         <v>101024.0</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C25" s="64" t="s">
         <v>24</v>
@@ -12849,10 +12885,10 @@
         <v>21</v>
       </c>
       <c r="M25" s="34" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O25" s="67"/>
       <c r="P25" s="68"/>
@@ -12886,7 +12922,7 @@
       <c r="Q26" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="68">
+      <c r="R26" s="37">
         <v>2.0</v>
       </c>
     </row>
@@ -12895,7 +12931,7 @@
         <v>1010251.0</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C27" s="64" t="s">
         <v>52</v>
@@ -12922,7 +12958,7 @@
         <v>1010252.0</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C28" s="64" t="s">
         <v>52</v>
@@ -12949,10 +12985,10 @@
         <v>101026.0</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D29" s="65">
         <v>0.0</v>
@@ -12964,7 +13000,7 @@
       <c r="G29" s="66"/>
       <c r="H29" s="62"/>
       <c r="I29" s="63" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J29" s="62">
         <v>5.5</v>
@@ -12976,10 +13012,10 @@
         <v>21</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O29" s="67"/>
       <c r="P29" s="68"/>
@@ -12991,7 +13027,7 @@
         <v>101027.0</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C30" s="64" t="s">
         <v>24</v>
@@ -13009,13 +13045,13 @@
       <c r="J30" s="62"/>
       <c r="K30" s="62"/>
       <c r="L30" s="34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O30" s="67"/>
       <c r="P30" s="68"/>
@@ -13027,7 +13063,7 @@
         <v>101028.0</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C31" s="64" t="s">
         <v>32</v>
@@ -13042,7 +13078,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="62"/>
       <c r="I31" s="63" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J31" s="62">
         <v>6.0</v>
@@ -13060,10 +13096,10 @@
         <v>101029.0</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D32" s="65">
         <v>2.0</v>
@@ -13074,10 +13110,10 @@
       <c r="F32" s="65"/>
       <c r="G32" s="66"/>
       <c r="H32" s="62" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I32" s="63" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J32" s="62">
         <v>5.5</v>
@@ -13086,13 +13122,13 @@
         <v>2.0</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N32" s="34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O32" s="67"/>
       <c r="P32" s="68"/>
@@ -13104,7 +13140,7 @@
         <v>101030.0</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C33" s="64" t="s">
         <v>40</v>
@@ -13131,7 +13167,7 @@
         <v>101031.0</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C34" s="64" t="s">
         <v>24</v>
@@ -13152,10 +13188,10 @@
         <v>21</v>
       </c>
       <c r="M34" s="34" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="N34" s="34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O34" s="67"/>
       <c r="P34" s="68"/>
@@ -13167,7 +13203,7 @@
         <v>101032.0</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C35" s="64" t="s">
         <v>40</v>
@@ -13194,7 +13230,7 @@
         <v>101033.0</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C36" s="64" t="s">
         <v>52</v>
@@ -13206,10 +13242,10 @@
         <v>101034.0</v>
       </c>
       <c r="F36" s="65" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G36" s="66" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H36" s="62"/>
       <c r="I36" s="63"/>
@@ -13225,7 +13261,7 @@
         <v>101034.0</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C37" s="64" t="s">
         <v>32</v>
@@ -13240,7 +13276,7 @@
       <c r="G37" s="66"/>
       <c r="H37" s="62"/>
       <c r="I37" s="63" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J37" s="62">
         <v>8.0</v>
@@ -13258,7 +13294,7 @@
         <v>101035.0</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C38" s="64" t="s">
         <v>18</v>
@@ -13267,7 +13303,7 @@
         <v>0.0</v>
       </c>
       <c r="E38" s="65" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F38" s="65"/>
       <c r="G38" s="66"/>
@@ -13285,7 +13321,7 @@
         <v>102001.0</v>
       </c>
       <c r="B39" s="71" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>32</v>
@@ -13294,7 +13330,7 @@
         <v>0.0</v>
       </c>
       <c r="I39" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J39" s="60">
         <v>6.0</v>
@@ -13308,7 +13344,7 @@
         <v>102002.0</v>
       </c>
       <c r="B40" s="71" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>32</v>
@@ -13317,10 +13353,10 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41">
@@ -13328,7 +13364,7 @@
         <v>102003.0</v>
       </c>
       <c r="B41" s="71" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>40</v>
@@ -13342,7 +13378,7 @@
         <v>102004.0</v>
       </c>
       <c r="B42" s="71" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>32</v>
@@ -13354,7 +13390,7 @@
         <v>21</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43">
@@ -13362,7 +13398,7 @@
         <v>102005.0</v>
       </c>
       <c r="B43" s="71" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>32</v>
@@ -13371,7 +13407,7 @@
         <v>0.0</v>
       </c>
       <c r="I43" s="61" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J43" s="6">
         <v>8.0</v>
@@ -13385,7 +13421,7 @@
         <v>102006.0</v>
       </c>
       <c r="B44" s="71" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>18</v>
@@ -13394,7 +13430,7 @@
         <v>0.0</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45">
@@ -13402,7 +13438,7 @@
         <v>103001.0</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>40</v>
@@ -13419,7 +13455,7 @@
         <v>103002.0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>32</v>
@@ -13432,7 +13468,7 @@
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J46" s="6">
         <v>6.0</v>
@@ -13446,7 +13482,7 @@
         <v>103003.0</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>52</v>
@@ -13458,10 +13494,10 @@
         <v>103004.0</v>
       </c>
       <c r="F47" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G47" s="58" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48">
@@ -13469,7 +13505,7 @@
         <v>103004.0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>52</v>
@@ -13481,10 +13517,10 @@
         <v>103005.0</v>
       </c>
       <c r="F48" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G48" s="58" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49">
@@ -13492,7 +13528,7 @@
         <v>103005.0</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>32</v>
@@ -13505,7 +13541,7 @@
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="61" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J49" s="6">
         <v>7.0</v>
@@ -13519,7 +13555,7 @@
         <v>103006.0</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>40</v>
@@ -13540,7 +13576,7 @@
         <v>103007.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>40</v>
@@ -13557,7 +13593,7 @@
         <v>103008.0</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>24</v>
@@ -13575,7 +13611,7 @@
         <v>39</v>
       </c>
       <c r="N52" s="55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
@@ -13583,7 +13619,7 @@
         <v>103009.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>24</v>
@@ -13595,13 +13631,13 @@
         <v>103010.0</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54">
@@ -13609,7 +13645,7 @@
         <v>103010.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>40</v>
@@ -13626,7 +13662,7 @@
         <v>103011.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>40</v>
@@ -13643,7 +13679,7 @@
         <v>103012.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>40</v>
@@ -13660,7 +13696,7 @@
         <v>103013.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>40</v>
@@ -13677,7 +13713,7 @@
         <v>103014.0</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>40</v>
@@ -13694,7 +13730,7 @@
         <v>103015.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>32</v>
@@ -13707,7 +13743,7 @@
       </c>
       <c r="H59" s="6"/>
       <c r="I59" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J59" s="6">
         <v>6.0</v>
@@ -13721,7 +13757,7 @@
         <v>103016.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>24</v>
@@ -13739,7 +13775,7 @@
         <v>31</v>
       </c>
       <c r="N60" s="55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61">
@@ -13747,10 +13783,10 @@
         <v>103017.0</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D61" s="6">
         <v>2.0</v>
@@ -13762,10 +13798,10 @@
         <v>21</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N61" s="55" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="S61" s="4">
         <v>0.5</v>
@@ -13776,7 +13812,7 @@
         <v>103018.0</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>52</v>
@@ -13788,10 +13824,10 @@
         <v>103019.0</v>
       </c>
       <c r="F62" s="57" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G62" s="58" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63">
@@ -13799,7 +13835,7 @@
         <v>103019.0</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>55</v>
@@ -13814,7 +13850,7 @@
         <v>29</v>
       </c>
       <c r="P63" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64">
@@ -13822,7 +13858,7 @@
         <v>103020.0</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>55</v>
@@ -13838,7 +13874,7 @@
         <v>29</v>
       </c>
       <c r="P64" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65">
@@ -13846,7 +13882,7 @@
         <v>103021.0</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>55</v>
@@ -13862,7 +13898,7 @@
         <v>29</v>
       </c>
       <c r="P65" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66">
@@ -13870,7 +13906,7 @@
         <v>103022.0</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>55</v>
@@ -13886,7 +13922,7 @@
         <v>29</v>
       </c>
       <c r="P66" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67">
@@ -13894,10 +13930,10 @@
         <v>103023.0</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D67" s="6">
         <v>0.0</v>
@@ -13907,7 +13943,7 @@
       </c>
       <c r="H67" s="60"/>
       <c r="I67" s="61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J67" s="60">
         <v>0.1</v>
@@ -13920,7 +13956,7 @@
         <v>29</v>
       </c>
       <c r="P67" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68">
@@ -13928,7 +13964,7 @@
         <v>103024.0</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>32</v>
@@ -13941,7 +13977,7 @@
       </c>
       <c r="H68" s="6"/>
       <c r="I68" s="61" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J68" s="6">
         <v>8.0</v>
@@ -13955,7 +13991,7 @@
         <v>103025.0</v>
       </c>
       <c r="B69" s="73" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>40</v>
@@ -13978,7 +14014,7 @@
         <v>0.0</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71">
@@ -13986,7 +14022,7 @@
         <v>104001.0</v>
       </c>
       <c r="B71" s="71" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>32</v>
@@ -13998,10 +14034,10 @@
         <v>104002.0</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72">
@@ -14009,7 +14045,7 @@
         <v>104002.0</v>
       </c>
       <c r="B72" s="71" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>32</v>
@@ -14021,7 +14057,7 @@
         <v>104003.0</v>
       </c>
       <c r="I72" s="61" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J72" s="6">
         <v>6.0</v>
@@ -14035,7 +14071,7 @@
         <v>104003.0</v>
       </c>
       <c r="B73" s="71" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>55</v>
@@ -14047,10 +14083,10 @@
         <v>104004.0</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P73" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="74">
@@ -14058,7 +14094,7 @@
         <v>104004.0</v>
       </c>
       <c r="B74" s="71" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>55</v>
@@ -14070,10 +14106,10 @@
         <v>104005.0</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P74" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75">
@@ -14081,10 +14117,10 @@
         <v>104005.0</v>
       </c>
       <c r="B75" s="71" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D75" s="6">
         <v>0.0</v>
@@ -14093,7 +14129,7 @@
         <v>104006.0</v>
       </c>
       <c r="I75" s="61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J75" s="60">
         <v>0.1</v>
@@ -14102,10 +14138,10 @@
         <v>-1.0</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P75" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76">
@@ -14116,7 +14152,7 @@
         <v>65</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D76" s="6">
         <v>0.0</v>
@@ -14128,12 +14164,12 @@
         <v>21</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J76" s="60"/>
       <c r="K76" s="60"/>
       <c r="Q76" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="R76" s="4">
         <v>2.0</v>
@@ -14144,7 +14180,7 @@
         <v>1040061.0</v>
       </c>
       <c r="B77" s="71" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C77" s="64" t="s">
         <v>52</v>
@@ -14161,7 +14197,7 @@
         <v>1040062.0</v>
       </c>
       <c r="B78" s="71" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C78" s="64" t="s">
         <v>52</v>
@@ -14178,10 +14214,10 @@
         <v>104007.0</v>
       </c>
       <c r="B79" s="71" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D79" s="6">
         <v>0.0</v>
@@ -14190,16 +14226,16 @@
         <v>104008.0</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P79" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80">
@@ -14207,7 +14243,7 @@
         <v>104008.0</v>
       </c>
       <c r="B80" s="71" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>55</v>
@@ -14219,10 +14255,10 @@
         <v>104009.0</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P80" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81">
@@ -14230,7 +14266,7 @@
         <v>104009.0</v>
       </c>
       <c r="B81" s="71" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>40</v>
@@ -14247,7 +14283,7 @@
         <v>104010.0</v>
       </c>
       <c r="B82" s="71" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>55</v>
@@ -14259,7 +14295,7 @@
         <v>104011.0</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83">
@@ -14267,7 +14303,7 @@
         <v>104011.0</v>
       </c>
       <c r="B83" s="71" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>32</v>
@@ -14277,6 +14313,12 @@
       </c>
       <c r="E83" s="6">
         <v>104012.0</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="84">
@@ -14284,7 +14326,7 @@
         <v>104012.0</v>
       </c>
       <c r="B84" s="71" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>18</v>
@@ -14293,7 +14335,7 @@
         <v>0.0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85">
@@ -14301,7 +14343,7 @@
         <v>201001.0</v>
       </c>
       <c r="B85" s="74" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>52</v>
@@ -14313,10 +14355,10 @@
         <v>201002.0</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H85" s="32"/>
       <c r="I85" s="32"/>
@@ -14327,7 +14369,7 @@
         <v>201002.0</v>
       </c>
       <c r="B86" s="74" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>52</v>
@@ -14339,10 +14381,10 @@
         <v>201003.0</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="32"/>
@@ -14353,10 +14395,10 @@
         <v>201003.0</v>
       </c>
       <c r="B87" s="74" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D87" s="6">
         <v>0.0</v>
@@ -14365,14 +14407,14 @@
         <v>201004.0</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H87" s="32"/>
       <c r="I87" s="60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J87" s="60">
         <v>0.05</v>
@@ -14386,7 +14428,7 @@
         <v>201004.0</v>
       </c>
       <c r="B88" s="74" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>52</v>
@@ -14398,10 +14440,10 @@
         <v>201005.0</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H88" s="32"/>
       <c r="I88" s="32"/>
@@ -14412,7 +14454,7 @@
         <v>201005.0</v>
       </c>
       <c r="B89" s="74" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>52</v>
@@ -14424,10 +14466,10 @@
         <v>201006.0</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="32"/>
@@ -14438,7 +14480,7 @@
         <v>201006.0</v>
       </c>
       <c r="B90" s="74" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>52</v>
@@ -14460,10 +14502,10 @@
         <v>201007.0</v>
       </c>
       <c r="B91" s="74" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D91" s="6">
         <v>0.0</v>
@@ -14475,7 +14517,7 @@
       <c r="G91" s="32"/>
       <c r="H91" s="32"/>
       <c r="I91" s="60" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J91" s="60">
         <v>6.5</v>
@@ -14489,10 +14531,10 @@
         <v>201008.0</v>
       </c>
       <c r="B92" s="74" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D92" s="6">
         <v>0.0</v>
@@ -14504,7 +14546,7 @@
       <c r="G92" s="32"/>
       <c r="H92" s="32"/>
       <c r="I92" s="60" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J92" s="60">
         <v>6.0</v>
@@ -14518,10 +14560,10 @@
         <v>201009.0</v>
       </c>
       <c r="B93" s="74" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D93" s="6">
         <v>0.0</v>
@@ -14533,7 +14575,7 @@
       <c r="G93" s="32"/>
       <c r="H93" s="32"/>
       <c r="I93" s="60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J93" s="60">
         <v>0.05</v>
@@ -14545,7 +14587,7 @@
         <v>21</v>
       </c>
       <c r="P93" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94">
@@ -14553,10 +14595,10 @@
         <v>201010.0</v>
       </c>
       <c r="B94" s="74" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D94" s="6">
         <v>0.0</v>
@@ -14565,14 +14607,14 @@
         <v>201011.0</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H94" s="32"/>
       <c r="I94" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J94" s="6">
         <v>7.0</v>
@@ -14586,7 +14628,7 @@
         <v>201011.0</v>
       </c>
       <c r="B95" s="75" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>52</v>
@@ -14598,10 +14640,10 @@
         <v>201012.0</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G95" s="76" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H95" s="32"/>
       <c r="I95" s="32"/>
@@ -14612,7 +14654,7 @@
         <v>201012.0</v>
       </c>
       <c r="B96" s="74" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>52</v>
@@ -14624,10 +14666,10 @@
         <v>201013.0</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="32"/>
@@ -14638,7 +14680,7 @@
         <v>201013.0</v>
       </c>
       <c r="B97" s="74" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>52</v>
@@ -14650,10 +14692,10 @@
         <v>201014.0</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="32"/>
@@ -14664,7 +14706,7 @@
         <v>201014.0</v>
       </c>
       <c r="B98" s="74" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>52</v>
@@ -14676,10 +14718,10 @@
         <v>201015.0</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="32"/>
@@ -14690,7 +14732,7 @@
         <v>201015.0</v>
       </c>
       <c r="B99" s="74" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>52</v>
@@ -14702,10 +14744,10 @@
         <v>201016.0</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="32"/>
@@ -14716,10 +14758,10 @@
         <v>201016.0</v>
       </c>
       <c r="B100" s="74" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D100" s="6">
         <v>0.0</v>
@@ -14738,7 +14780,7 @@
         <v>2010161.0</v>
       </c>
       <c r="B101" s="74" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>52</v>
@@ -14760,7 +14802,7 @@
         <v>2010162.0</v>
       </c>
       <c r="B102" s="74" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>52</v>
@@ -14782,7 +14824,7 @@
         <v>201017.0</v>
       </c>
       <c r="B103" s="74" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>52</v>
@@ -14794,10 +14836,10 @@
         <v>201018.0</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H103" s="32"/>
       <c r="I103" s="32"/>
@@ -14808,7 +14850,7 @@
         <v>201018.0</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>52</v>
@@ -14820,10 +14862,10 @@
         <v>201016.0</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="32"/>
@@ -14834,7 +14876,7 @@
         <v>201019.0</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>52</v>
@@ -14846,10 +14888,10 @@
         <v>201020.0</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="32"/>
@@ -14860,7 +14902,7 @@
         <v>201020.0</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>52</v>
@@ -14872,10 +14914,10 @@
         <v>201016.0</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="32"/>
@@ -14886,7 +14928,7 @@
         <v>201021.0</v>
       </c>
       <c r="B107" s="74" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>52</v>
@@ -14898,10 +14940,10 @@
         <v>201022.0</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G107" s="76" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="32"/>
@@ -14912,7 +14954,7 @@
         <v>201022.0</v>
       </c>
       <c r="B108" s="74" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>52</v>
@@ -14924,10 +14966,10 @@
         <v>201023.0</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="32"/>
@@ -14938,7 +14980,7 @@
         <v>201023.0</v>
       </c>
       <c r="B109" s="74" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>52</v>
@@ -14950,10 +14992,10 @@
         <v>201024.0</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="32"/>
@@ -14964,7 +15006,7 @@
         <v>201024.0</v>
       </c>
       <c r="B110" s="74" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>52</v>
@@ -14976,10 +15018,10 @@
         <v>201025.0</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="32"/>
@@ -14990,7 +15032,7 @@
         <v>201025.0</v>
       </c>
       <c r="B111" s="74" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>52</v>
@@ -15002,10 +15044,10 @@
         <v>201026.0</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="32"/>
@@ -15016,7 +15058,7 @@
         <v>201026.0</v>
       </c>
       <c r="B112" s="74" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>52</v>
@@ -15028,10 +15070,10 @@
         <v>201027.0</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="32"/>
@@ -15042,7 +15084,7 @@
         <v>201027.0</v>
       </c>
       <c r="B113" s="74" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>52</v>
@@ -15054,10 +15096,10 @@
         <v>201028.0</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="32"/>
@@ -15068,7 +15110,7 @@
         <v>201028.0</v>
       </c>
       <c r="B114" s="74" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>52</v>
@@ -15080,10 +15122,10 @@
         <v>201029.0</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="32"/>
@@ -15094,7 +15136,7 @@
         <v>201029.0</v>
       </c>
       <c r="B115" s="74" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>52</v>
@@ -15106,10 +15148,10 @@
         <v>201030.0</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="32"/>
@@ -15120,7 +15162,7 @@
         <v>201030.0</v>
       </c>
       <c r="B116" s="74" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>52</v>
@@ -15132,10 +15174,10 @@
         <v>201031.0</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="32"/>
@@ -15146,7 +15188,7 @@
         <v>201031.0</v>
       </c>
       <c r="B117" s="74" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>52</v>
@@ -15158,10 +15200,10 @@
         <v>201032.0</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H117" s="32"/>
       <c r="I117" s="32"/>
@@ -15172,7 +15214,7 @@
         <v>201032.0</v>
       </c>
       <c r="B118" s="74" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>52</v>
@@ -15184,10 +15226,10 @@
         <v>201033.0</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="32"/>
@@ -15198,7 +15240,7 @@
         <v>201033.0</v>
       </c>
       <c r="B119" s="74" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>52</v>
@@ -15210,10 +15252,10 @@
         <v>201034.0</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="32"/>
@@ -15224,7 +15266,7 @@
         <v>201034.0</v>
       </c>
       <c r="B120" s="74" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>52</v>
@@ -15236,10 +15278,10 @@
         <v>201035.0</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="32"/>
@@ -15250,7 +15292,7 @@
         <v>201035.0</v>
       </c>
       <c r="B121" s="74" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>40</v>
@@ -15272,7 +15314,7 @@
         <v>201036.0</v>
       </c>
       <c r="B122" s="74" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>52</v>
@@ -15284,10 +15326,10 @@
         <v>201037.0</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="32"/>
@@ -15298,7 +15340,7 @@
         <v>201037.0</v>
       </c>
       <c r="B123" s="74" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>32</v>
@@ -15320,7 +15362,7 @@
         <v>201038.0</v>
       </c>
       <c r="B124" s="74" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>52</v>
@@ -15332,10 +15374,10 @@
         <v>201039.0</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H124" s="32"/>
       <c r="I124" s="32"/>
@@ -15346,7 +15388,7 @@
         <v>201039.0</v>
       </c>
       <c r="B125" s="74" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>40</v>
@@ -15368,10 +15410,10 @@
         <v>201040.0</v>
       </c>
       <c r="B126" s="74" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D126" s="6">
         <v>0.0</v>
@@ -15382,10 +15424,10 @@
       <c r="F126" s="32"/>
       <c r="G126" s="32"/>
       <c r="H126" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I126" s="60" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J126" s="60">
         <v>6.0</v>
@@ -15394,10 +15436,10 @@
         <v>2.0</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P126" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="127">
@@ -15405,7 +15447,7 @@
         <v>201041.0</v>
       </c>
       <c r="B127" s="74" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>55</v>
@@ -15422,10 +15464,10 @@
       <c r="I127" s="32"/>
       <c r="J127" s="32"/>
       <c r="O127" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P127" s="37" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="128">
@@ -15433,7 +15475,7 @@
         <v>201042.0</v>
       </c>
       <c r="B128" s="77" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>18</v>
@@ -15442,7 +15484,7 @@
         <v>0.0</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>

--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="257">
   <si>
     <t>To. 개발 : 스크립트 수정 시, 파란색으로 칠해둘 것!!</t>
   </si>
@@ -292,6 +292,9 @@
     <t>뭐라도 하겠지</t>
   </si>
   <si>
+    <t>[Parallel]</t>
+  </si>
+  <si>
     <t>0으로 해두면 동시에 됨 / 0.5 = 앞에 거 0.5초 뒤에 다음 거 재생</t>
   </si>
   <si>
@@ -299,6 +302,12 @@
   </si>
   <si>
     <t>선택지, 스크립트, 이벤트(클릭 등) 이 3개는 직렬로만 선택이 됨</t>
+  </si>
+  <si>
+    <t>기준이 되는 행이 위에 있고</t>
+  </si>
+  <si>
+    <t>거기에 병렬 처리할 행에만 키워드 넣으면 됩니당!!</t>
   </si>
   <si>
     <t>비고</t>
@@ -458,7 +467,13 @@
     <t>{fade a=3.5}누...누구야...!!!</t>
   </si>
   <si>
+    <t>수풀 카메라 쉬프트</t>
+  </si>
+  <si>
     <t>수풀에게 줌 땡김</t>
+  </si>
+  <si>
+    <t>Camera, Parallel</t>
   </si>
   <si>
     <t>수풀에게 줌 땡김 x 2</t>
@@ -522,6 +537,9 @@
     <t>고양이 쓰다듬 당하기</t>
   </si>
   <si>
+    <t>Animation, Parallel</t>
+  </si>
+  <si>
     <t>Cat_Pet</t>
   </si>
   <si>
@@ -540,6 +558,9 @@
     <t>고양이 점프하면서 안나 덮치기</t>
   </si>
   <si>
+    <t>Cat_Knockback</t>
+  </si>
+  <si>
     <t>안나 뒤로 넘어지기</t>
   </si>
   <si>
@@ -588,7 +609,7 @@
     <t>줌인</t>
   </si>
   <si>
-    <t>{fade a=3.5} 후 아무리 쫓아와도 그 가위는 안 보이는 것 같네</t>
+    <t>{fade a=3.5} 후 그 고양이는 못 찾겠네...</t>
   </si>
   <si>
     <t>Anna_Sigh</t>
@@ -637,9 +658,6 @@
   </si>
   <si>
     <t>안나 놀라는 애니메이션</t>
-  </si>
-  <si>
-    <t>Animation, Parallel</t>
   </si>
   <si>
     <t>{fade a=3.5} 으악 저건 뭐야?!!</t>
@@ -856,7 +874,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -964,12 +982,22 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.0"/>
       <color rgb="FF0000FF"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+    </font>
+    <font>
+      <color rgb="FFFF00FF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1107,7 +1135,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="82">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1294,6 +1322,12 @@
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -1307,6 +1341,9 @@
     <xf borderId="0" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
@@ -1316,22 +1353,25 @@
     <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1354,7 +1394,7 @@
     <xdr:ext cx="3524250" cy="695325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1382,7 +1422,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2026,19 +2066,34 @@
       <c r="F25" s="30"/>
       <c r="G25" s="30"/>
     </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2082,7 +2137,7 @@
         <v>NextID</v>
       </c>
       <c r="E1" s="31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -2141,7 +2196,7 @@
         <v>101004</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -2162,7 +2217,7 @@
         <v>101005</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -2221,7 +2276,7 @@
         <v>101008</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -2242,7 +2297,7 @@
         <v>101009</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -2263,7 +2318,7 @@
         <v>101010</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -2284,7 +2339,7 @@
         <v>101011</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -2305,7 +2360,7 @@
         <v>101012</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -2326,7 +2381,7 @@
         <v>101013</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
@@ -2347,7 +2402,7 @@
         <v>101014</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -2368,7 +2423,7 @@
         <v>101015</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -2389,7 +2444,7 @@
         <v>101016</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -2401,16 +2456,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
         <v>Camera</v>
       </c>
-      <c r="C17" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
+      <c r="C17" s="6"/>
       <c r="D17" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101017.0)</f>
         <v>101017</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -2419,19 +2471,19 @@
         <v>101017</v>
       </c>
       <c r="B18" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera, Parallel")</f>
+        <v>Camera, Parallel</v>
       </c>
       <c r="C18" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="D18" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101018.0)</f>
         <v>101018</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -2440,12 +2492,12 @@
         <v>101018</v>
       </c>
       <c r="B19" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Event")</f>
-        <v>Animation, Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C19" s="32">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="D19" s="32">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101019.0)</f>
@@ -2459,8 +2511,8 @@
         <v>101019</v>
       </c>
       <c r="B20" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
-        <v>Bubble, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Event")</f>
+        <v>Animation, Event</v>
       </c>
       <c r="C20" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2471,7 +2523,7 @@
         <v>101020</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -2480,8 +2532,8 @@
         <v>101020</v>
       </c>
       <c r="B21" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
-        <v>Animation</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
+        <v>Bubble, Camera</v>
       </c>
       <c r="C21" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2498,8 +2550,8 @@
         <v>101021</v>
       </c>
       <c r="B22" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
+        <v>Animation</v>
       </c>
       <c r="C22" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2516,8 +2568,8 @@
         <v>101022</v>
       </c>
       <c r="B23" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
-        <v>Animation</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C23" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2556,15 +2608,15 @@
         <v>Animation</v>
       </c>
       <c r="C25" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D25" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101025.0)</f>
         <v>101025</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
@@ -2573,40 +2625,40 @@
         <v>101025</v>
       </c>
       <c r="B26" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
+        <v>Animation</v>
+      </c>
+      <c r="C26" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D26" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
+        <v>101026</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
+        <v>101026</v>
+      </c>
+      <c r="B27" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Select")</f>
         <v>Select</v>
-      </c>
-      <c r="C26" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010251.0)</f>
-        <v>1010251</v>
-      </c>
-      <c r="B27" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
       </c>
       <c r="C27" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D27" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
-        <v>101026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="32">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010252.0)</f>
-        <v>1010252</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010261.0)</f>
+        <v>1010261</v>
       </c>
       <c r="B28" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -2617,26 +2669,26 @@
         <v>0</v>
       </c>
       <c r="D28" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101029.0)</f>
-        <v>101029</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101027.0)</f>
+        <v>101027</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="32">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
-        <v>101026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010262.0)</f>
+        <v>1010262</v>
       </c>
       <c r="B29" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Camera")</f>
-        <v>Animation, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C29" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D29" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010267.0)</f>
-        <v>1010267</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101030.0)</f>
+        <v>101030</v>
       </c>
     </row>
     <row r="30">
@@ -2645,8 +2697,8 @@
         <v>101027</v>
       </c>
       <c r="B30" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
-        <v>Animation</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Camera")</f>
+        <v>Animation, Camera</v>
       </c>
       <c r="C30" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2663,16 +2715,16 @@
         <v>101028</v>
       </c>
       <c r="B31" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Parallel")</f>
+        <v>Animation, Parallel</v>
       </c>
       <c r="C31" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D31" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101025.0)</f>
-        <v>101025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101029.0)</f>
+        <v>101029</v>
       </c>
     </row>
     <row r="32">
@@ -2681,16 +2733,16 @@
         <v>101029</v>
       </c>
       <c r="B32" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Camera")</f>
-        <v>Animation, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C32" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D32" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101030.0)</f>
-        <v>101030</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
+        <v>101026</v>
       </c>
     </row>
     <row r="33">
@@ -2699,12 +2751,12 @@
         <v>101030</v>
       </c>
       <c r="B33" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Camera")</f>
+        <v>Animation, Camera</v>
       </c>
       <c r="C33" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="D33" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101031.0)</f>
@@ -2735,8 +2787,8 @@
         <v>101032</v>
       </c>
       <c r="B35" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Parallel")</f>
+        <v>Animation, Parallel</v>
       </c>
       <c r="C35" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2753,8 +2805,8 @@
         <v>101033</v>
       </c>
       <c r="B36" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C36" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2771,8 +2823,8 @@
         <v>101034</v>
       </c>
       <c r="B37" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C37" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2789,23 +2841,26 @@
         <v>101035</v>
       </c>
       <c r="B38" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
-        <v>End</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C38" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="34"/>
+      <c r="D38" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101036.0)</f>
+        <v>101036</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102001.0)</f>
-        <v>102001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101036.0)</f>
+        <v>101036</v>
       </c>
       <c r="B39" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
+        <v>End</v>
       </c>
       <c r="C39" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2815,8 +2870,8 @@
     </row>
     <row r="40">
       <c r="A40" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102002.0)</f>
-        <v>102002</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102001.0)</f>
+        <v>102001</v>
       </c>
       <c r="B40" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
@@ -2830,12 +2885,12 @@
     </row>
     <row r="41">
       <c r="A41" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102003.0)</f>
-        <v>102003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102002.0)</f>
+        <v>102002</v>
       </c>
       <c r="B41" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera, Parallel")</f>
+        <v>Camera, Parallel</v>
       </c>
       <c r="C41" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2845,12 +2900,12 @@
     </row>
     <row r="42">
       <c r="A42" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102004.0)</f>
-        <v>102004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102003.0)</f>
+        <v>102003</v>
       </c>
       <c r="B42" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C42" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2860,8 +2915,8 @@
     </row>
     <row r="43">
       <c r="A43" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102005.0)</f>
-        <v>102005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102004.0)</f>
+        <v>102004</v>
       </c>
       <c r="B43" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
@@ -2875,12 +2930,12 @@
     </row>
     <row r="44">
       <c r="A44" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102006.0)</f>
-        <v>102006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102005.0)</f>
+        <v>102005</v>
       </c>
       <c r="B44" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
-        <v>End</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C44" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2890,62 +2945,59 @@
     </row>
     <row r="45">
       <c r="A45" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102006.0)</f>
+        <v>102006</v>
+      </c>
+      <c r="B45" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
+        <v>End</v>
+      </c>
+      <c r="C45" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="34"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103001.0)</f>
         <v>103001</v>
       </c>
-      <c r="B45" s="34" t="str">
+      <c r="B46" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
         <v>Event</v>
-      </c>
-      <c r="C45" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103002.0)</f>
-        <v>103002</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103002.0)</f>
-        <v>103002</v>
-      </c>
-      <c r="B46" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
       </c>
       <c r="C46" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
       <c r="D46" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103002.0)</f>
+        <v>103002</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103002.0)</f>
+        <v>103002</v>
+      </c>
+      <c r="B47" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
+      </c>
+      <c r="C47" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103003.0)</f>
         <v>103003</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="34">
+    <row r="48">
+      <c r="A48" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103003.0)</f>
         <v>103003</v>
-      </c>
-      <c r="B47" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
-      </c>
-      <c r="C47" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103004.0)</f>
-        <v>103004</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103004.0)</f>
-        <v>103004</v>
       </c>
       <c r="B48" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -2956,50 +3008,50 @@
         <v>0</v>
       </c>
       <c r="D48" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103005.0)</f>
-        <v>103005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103004.0)</f>
+        <v>103004</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103005.0)</f>
-        <v>103005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103004.0)</f>
+        <v>103004</v>
       </c>
       <c r="B49" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C49" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D49" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103006.0)</f>
-        <v>103006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103005.0)</f>
+        <v>103005</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103006.0)</f>
-        <v>103006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103005.0)</f>
+        <v>103005</v>
       </c>
       <c r="B50" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C50" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D50" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103007.0)</f>
-        <v>103007</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103006.0)</f>
+        <v>103006</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103007.0)</f>
-        <v>103007</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103006.0)</f>
+        <v>103006</v>
       </c>
       <c r="B51" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
@@ -3010,68 +3062,68 @@
         <v>0</v>
       </c>
       <c r="D51" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103007.0)</f>
+        <v>103007</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103007.0)</f>
+        <v>103007</v>
+      </c>
+      <c r="B52" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
+      </c>
+      <c r="C52" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103008.0)</f>
         <v>103008</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="34">
+    <row r="53">
+      <c r="A53" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103008.0)</f>
         <v>103008</v>
-      </c>
-      <c r="B52" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
-        <v>Animation</v>
-      </c>
-      <c r="C52" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="D52" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103009.0)</f>
-        <v>103009</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103009.0)</f>
-        <v>103009</v>
       </c>
       <c r="B53" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
         <v>Animation</v>
       </c>
       <c r="C53" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="D53" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103010.0)</f>
-        <v>103010</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103009.0)</f>
+        <v>103009</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103010.0)</f>
-        <v>103010</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103009.0)</f>
+        <v>103009</v>
       </c>
       <c r="B54" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
+        <v>Animation</v>
       </c>
       <c r="C54" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D54" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103011.0)</f>
-        <v>103011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103010.0)</f>
+        <v>103010</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103011.0)</f>
-        <v>103011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103010.0)</f>
+        <v>103010</v>
       </c>
       <c r="B55" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
@@ -3082,14 +3134,14 @@
         <v>0</v>
       </c>
       <c r="D55" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103012.0)</f>
-        <v>103012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103011.0)</f>
+        <v>103011</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103012.0)</f>
-        <v>103012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103011.0)</f>
+        <v>103011</v>
       </c>
       <c r="B56" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
@@ -3100,14 +3152,14 @@
         <v>0</v>
       </c>
       <c r="D56" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103013.0)</f>
-        <v>103013</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103012.0)</f>
+        <v>103012</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103013.0)</f>
-        <v>103013</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103012.0)</f>
+        <v>103012</v>
       </c>
       <c r="B57" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
@@ -3118,14 +3170,14 @@
         <v>0</v>
       </c>
       <c r="D57" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103014.0)</f>
-        <v>103014</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103013.0)</f>
+        <v>103013</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103014.0)</f>
-        <v>103014</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103013.0)</f>
+        <v>103013</v>
       </c>
       <c r="B58" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
@@ -3136,104 +3188,104 @@
         <v>0</v>
       </c>
       <c r="D58" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103015.0)</f>
-        <v>103015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103014.0)</f>
+        <v>103014</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103015.0)</f>
-        <v>103015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103014.0)</f>
+        <v>103014</v>
       </c>
       <c r="B59" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C59" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D59" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103016.0)</f>
-        <v>103016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103015.0)</f>
+        <v>103015</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103016.0)</f>
-        <v>103016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103015.0)</f>
+        <v>103015</v>
       </c>
       <c r="B60" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
-        <v>Animation</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C60" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D60" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103016.0)</f>
+        <v>103016</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103016.0)</f>
+        <v>103016</v>
+      </c>
+      <c r="B61" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation")</f>
+        <v>Animation</v>
+      </c>
+      <c r="C61" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103017.0)</f>
         <v>103017</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="34">
+    <row r="62">
+      <c r="A62" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103017.0)</f>
         <v>103017</v>
       </c>
-      <c r="B61" s="34" t="str">
+      <c r="B62" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Animation, Parallel")</f>
         <v>Animation, Parallel</v>
       </c>
-      <c r="C61" s="34">
+      <c r="C62" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="D61" s="34">
+      <c r="D62" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103018.0)</f>
         <v>103018</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="34">
+    <row r="63">
+      <c r="A63" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103018.0)</f>
         <v>103018</v>
       </c>
-      <c r="B62" s="34" t="str">
+      <c r="B63" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
         <v>Script</v>
-      </c>
-      <c r="C62" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103019.0)</f>
-        <v>103019</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103019.0)</f>
-        <v>103019</v>
-      </c>
-      <c r="B63" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
-        <v>Bubble</v>
       </c>
       <c r="C63" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D63" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103020.0)</f>
-        <v>103020</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103019.0)</f>
+        <v>103019</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103020.0)</f>
-        <v>103020</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103019.0)</f>
+        <v>103019</v>
       </c>
       <c r="B64" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
@@ -3244,14 +3296,14 @@
         <v>0</v>
       </c>
       <c r="D64" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103021.0)</f>
-        <v>103021</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103020.0)</f>
+        <v>103020</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103021.0)</f>
-        <v>103021</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103020.0)</f>
+        <v>103020</v>
       </c>
       <c r="B65" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
@@ -3262,14 +3314,14 @@
         <v>0</v>
       </c>
       <c r="D65" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103022.0)</f>
-        <v>103022</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103021.0)</f>
+        <v>103021</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103022.0)</f>
-        <v>103022</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103021.0)</f>
+        <v>103021</v>
       </c>
       <c r="B66" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
@@ -3280,101 +3332,101 @@
         <v>0</v>
       </c>
       <c r="D66" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103023.0)</f>
-        <v>103023</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103022.0)</f>
+        <v>103022</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103023.0)</f>
-        <v>103023</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103022.0)</f>
+        <v>103022</v>
       </c>
       <c r="B67" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
-        <v>Bubble, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
+        <v>Bubble</v>
       </c>
       <c r="C67" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D67" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103024.0)</f>
-        <v>103024</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103023.0)</f>
+        <v>103023</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103024.0)</f>
-        <v>103024</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103023.0)</f>
+        <v>103023</v>
       </c>
       <c r="B68" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
+        <v>Bubble, Camera</v>
       </c>
       <c r="C68" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103025.0)</f>
-        <v>103025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103024.0)</f>
+        <v>103024</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103025.0)</f>
-        <v>103025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103024.0)</f>
+        <v>103024</v>
       </c>
       <c r="B69" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C69" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103026.0)</f>
-        <v>103026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103025.0)</f>
+        <v>103025</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103026.0)</f>
-        <v>103026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103025.0)</f>
+        <v>103025</v>
       </c>
       <c r="B70" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
-        <v>End</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C70" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D70" s="34"/>
+      <c r="D70" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103026.0)</f>
+        <v>103026</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104001.0)</f>
-        <v>104001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103026.0)</f>
+        <v>103026</v>
       </c>
       <c r="B71" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
+        <v>End</v>
       </c>
       <c r="C71" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D71" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104002.0)</f>
-        <v>104002</v>
-      </c>
+      <c r="D71" s="34"/>
     </row>
     <row r="72">
       <c r="A72" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104002.0)</f>
-        <v>104002</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104001.0)</f>
+        <v>104001</v>
       </c>
       <c r="B72" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
@@ -3385,32 +3437,32 @@
         <v>0</v>
       </c>
       <c r="D72" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104003.0)</f>
-        <v>104003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104002.0)</f>
+        <v>104002</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104003.0)</f>
-        <v>104003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104002.0)</f>
+        <v>104002</v>
       </c>
       <c r="B73" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
-        <v>Bubble</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C73" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D73" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104004.0)</f>
-        <v>104004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104003.0)</f>
+        <v>104003</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104004.0)</f>
-        <v>104004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104003.0)</f>
+        <v>104003</v>
       </c>
       <c r="B74" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
@@ -3421,68 +3473,68 @@
         <v>0</v>
       </c>
       <c r="D74" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104005.0)</f>
-        <v>104005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104004.0)</f>
+        <v>104004</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104005.0)</f>
-        <v>104005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104004.0)</f>
+        <v>104004</v>
       </c>
       <c r="B75" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
-        <v>Bubble, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
+        <v>Bubble</v>
       </c>
       <c r="C75" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D75" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104006.0)</f>
-        <v>104006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104005.0)</f>
+        <v>104005</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104006.0)</f>
-        <v>104006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104005.0)</f>
+        <v>104005</v>
       </c>
       <c r="B76" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera, Select")</f>
-        <v>Camera, Select</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
+        <v>Bubble, Camera</v>
       </c>
       <c r="C76" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D76" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104006.0)</f>
+        <v>104006</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1040061.0)</f>
-        <v>1040061</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104006.0)</f>
+        <v>104006</v>
       </c>
       <c r="B77" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera, Select")</f>
+        <v>Camera, Select</v>
       </c>
       <c r="C77" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D77" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104007.0)</f>
-        <v>104007</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1040062.0)</f>
-        <v>1040062</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1040061.0)</f>
+        <v>1040061</v>
       </c>
       <c r="B78" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3499,131 +3551,131 @@
     </row>
     <row r="79">
       <c r="A79" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104007.0)</f>
-        <v>104007</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1040062.0)</f>
+        <v>1040062</v>
       </c>
       <c r="B79" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
-        <v>Bubble, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C79" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D79" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104008.0)</f>
-        <v>104008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104007.0)</f>
+        <v>104007</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104008.0)</f>
-        <v>104008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104007.0)</f>
+        <v>104007</v>
       </c>
       <c r="B80" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
-        <v>Bubble</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
+        <v>Bubble, Camera</v>
       </c>
       <c r="C80" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D80" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104009.0)</f>
-        <v>104009</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104008.0)</f>
+        <v>104008</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104009.0)</f>
-        <v>104009</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104008.0)</f>
+        <v>104008</v>
       </c>
       <c r="B81" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
+        <v>Bubble</v>
       </c>
       <c r="C81" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D81" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104010.0)</f>
-        <v>104010</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104009.0)</f>
+        <v>104009</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104010.0)</f>
-        <v>104010</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104009.0)</f>
+        <v>104009</v>
       </c>
       <c r="B82" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
-        <v>Bubble</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C82" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D82" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
-        <v>104011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104010.0)</f>
+        <v>104010</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
-        <v>104011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104010.0)</f>
+        <v>104010</v>
       </c>
       <c r="B83" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
+        <v>Bubble</v>
       </c>
       <c r="C83" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D83" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104012.0)</f>
-        <v>104012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
+        <v>104011</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104012.0)</f>
-        <v>104012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
+        <v>104011</v>
       </c>
       <c r="B84" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
-        <v>End</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C84" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D84" s="34"/>
+      <c r="D84" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104012.0)</f>
+        <v>104012</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201001.0)</f>
-        <v>201001</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104012.0)</f>
+        <v>104012</v>
       </c>
       <c r="B85" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
+        <v>End</v>
       </c>
       <c r="C85" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D85" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201002.0)</f>
-        <v>201002</v>
-      </c>
+      <c r="D85" s="34"/>
     </row>
     <row r="86">
       <c r="A86" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201002.0)</f>
-        <v>201002</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201001.0)</f>
+        <v>201001</v>
       </c>
       <c r="B86" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3634,50 +3686,50 @@
         <v>0</v>
       </c>
       <c r="D86" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201003.0)</f>
-        <v>201003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201002.0)</f>
+        <v>201002</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201003.0)</f>
-        <v>201003</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201002.0)</f>
+        <v>201002</v>
       </c>
       <c r="B87" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
-        <v>Script, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C87" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D87" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201004.0)</f>
-        <v>201004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201003.0)</f>
+        <v>201003</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201004.0)</f>
-        <v>201004</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201003.0)</f>
+        <v>201003</v>
       </c>
       <c r="B88" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
+        <v>Script, Camera</v>
       </c>
       <c r="C88" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D88" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201005.0)</f>
-        <v>201005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201004.0)</f>
+        <v>201004</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201005.0)</f>
-        <v>201005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201004.0)</f>
+        <v>201004</v>
       </c>
       <c r="B89" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3688,14 +3740,14 @@
         <v>0</v>
       </c>
       <c r="D89" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201006.0)</f>
-        <v>201006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201005.0)</f>
+        <v>201005</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201006.0)</f>
-        <v>201006</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201005.0)</f>
+        <v>201005</v>
       </c>
       <c r="B90" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3706,32 +3758,32 @@
         <v>0</v>
       </c>
       <c r="D90" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201007.0)</f>
-        <v>201007</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201006.0)</f>
+        <v>201006</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201007.0)</f>
-        <v>201007</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201006.0)</f>
+        <v>201006</v>
       </c>
       <c r="B91" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
-        <v>Script, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C91" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D91" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201008.0)</f>
-        <v>201008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201007.0)</f>
+        <v>201007</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201008.0)</f>
-        <v>201008</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201007.0)</f>
+        <v>201007</v>
       </c>
       <c r="B92" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
@@ -3742,68 +3794,68 @@
         <v>0</v>
       </c>
       <c r="D92" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201009.0)</f>
-        <v>201009</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201008.0)</f>
+        <v>201008</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201009.0)</f>
-        <v>201009</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201008.0)</f>
+        <v>201008</v>
       </c>
       <c r="B93" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
-        <v>Bubble, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
+        <v>Script, Camera</v>
       </c>
       <c r="C93" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D93" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201010.0)</f>
-        <v>201010</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201009.0)</f>
+        <v>201009</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201010.0)</f>
-        <v>201010</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201009.0)</f>
+        <v>201009</v>
       </c>
       <c r="B94" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
-        <v>Script, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
+        <v>Bubble, Camera</v>
       </c>
       <c r="C94" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D94" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201011.0)</f>
-        <v>201011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201010.0)</f>
+        <v>201010</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201011.0)</f>
-        <v>201011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201010.0)</f>
+        <v>201010</v>
       </c>
       <c r="B95" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
+        <v>Script, Camera</v>
       </c>
       <c r="C95" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D95" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201012.0)</f>
-        <v>201012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201011.0)</f>
+        <v>201011</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201012.0)</f>
-        <v>201012</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201011.0)</f>
+        <v>201011</v>
       </c>
       <c r="B96" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3814,14 +3866,14 @@
         <v>0</v>
       </c>
       <c r="D96" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201013.0)</f>
-        <v>201013</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201012.0)</f>
+        <v>201012</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201013.0)</f>
-        <v>201013</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201012.0)</f>
+        <v>201012</v>
       </c>
       <c r="B97" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3832,14 +3884,14 @@
         <v>0</v>
       </c>
       <c r="D97" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201014.0)</f>
-        <v>201014</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201013.0)</f>
+        <v>201013</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201014.0)</f>
-        <v>201014</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201013.0)</f>
+        <v>201013</v>
       </c>
       <c r="B98" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3850,14 +3902,14 @@
         <v>0</v>
       </c>
       <c r="D98" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201015.0)</f>
-        <v>201015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201014.0)</f>
+        <v>201014</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201015.0)</f>
-        <v>201015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201014.0)</f>
+        <v>201014</v>
       </c>
       <c r="B99" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3868,50 +3920,50 @@
         <v>0</v>
       </c>
       <c r="D99" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
-        <v>201016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201015.0)</f>
+        <v>201015</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
-        <v>201016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201015.0)</f>
+        <v>201015</v>
       </c>
       <c r="B100" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera, Select")</f>
-        <v>Camera, Select</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C100" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D100" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
+        <v>201016</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2010161.0)</f>
-        <v>2010161</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
+        <v>201016</v>
       </c>
       <c r="B101" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera, Select")</f>
+        <v>Camera, Select</v>
       </c>
       <c r="C101" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D101" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201017.0)</f>
-        <v>201017</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2010162.0)</f>
-        <v>2010162</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2010161.0)</f>
+        <v>2010161</v>
       </c>
       <c r="B102" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3922,14 +3974,14 @@
         <v>0</v>
       </c>
       <c r="D102" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201019.0)</f>
-        <v>201019</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201017.0)</f>
+        <v>201017</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201017.0)</f>
-        <v>201017</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2010162.0)</f>
+        <v>2010162</v>
       </c>
       <c r="B103" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3940,14 +3992,14 @@
         <v>0</v>
       </c>
       <c r="D103" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201018.0)</f>
-        <v>201018</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201019.0)</f>
+        <v>201019</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201018.0)</f>
-        <v>201018</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201017.0)</f>
+        <v>201017</v>
       </c>
       <c r="B104" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3958,14 +4010,14 @@
         <v>0</v>
       </c>
       <c r="D104" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
-        <v>201016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201018.0)</f>
+        <v>201018</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201019.0)</f>
-        <v>201019</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201018.0)</f>
+        <v>201018</v>
       </c>
       <c r="B105" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3976,14 +4028,14 @@
         <v>0</v>
       </c>
       <c r="D105" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201020.0)</f>
-        <v>201020</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
+        <v>201016</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201020.0)</f>
-        <v>201020</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201019.0)</f>
+        <v>201019</v>
       </c>
       <c r="B106" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -3994,14 +4046,14 @@
         <v>0</v>
       </c>
       <c r="D106" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
-        <v>201016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201020.0)</f>
+        <v>201020</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201021.0)</f>
-        <v>201021</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201020.0)</f>
+        <v>201020</v>
       </c>
       <c r="B107" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4012,14 +4064,14 @@
         <v>0</v>
       </c>
       <c r="D107" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201022.0)</f>
-        <v>201022</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
+        <v>201016</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201022.0)</f>
-        <v>201022</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201021.0)</f>
+        <v>201021</v>
       </c>
       <c r="B108" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4030,14 +4082,14 @@
         <v>0</v>
       </c>
       <c r="D108" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201023.0)</f>
-        <v>201023</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201022.0)</f>
+        <v>201022</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201023.0)</f>
-        <v>201023</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201022.0)</f>
+        <v>201022</v>
       </c>
       <c r="B109" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4048,14 +4100,14 @@
         <v>0</v>
       </c>
       <c r="D109" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201024.0)</f>
-        <v>201024</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201023.0)</f>
+        <v>201023</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201024.0)</f>
-        <v>201024</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201023.0)</f>
+        <v>201023</v>
       </c>
       <c r="B110" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4066,14 +4118,14 @@
         <v>0</v>
       </c>
       <c r="D110" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201025.0)</f>
-        <v>201025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201024.0)</f>
+        <v>201024</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201025.0)</f>
-        <v>201025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201024.0)</f>
+        <v>201024</v>
       </c>
       <c r="B111" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4084,14 +4136,14 @@
         <v>0</v>
       </c>
       <c r="D111" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201026.0)</f>
-        <v>201026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201025.0)</f>
+        <v>201025</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201026.0)</f>
-        <v>201026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201025.0)</f>
+        <v>201025</v>
       </c>
       <c r="B112" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4102,14 +4154,14 @@
         <v>0</v>
       </c>
       <c r="D112" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201027.0)</f>
-        <v>201027</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201026.0)</f>
+        <v>201026</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201027.0)</f>
-        <v>201027</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201026.0)</f>
+        <v>201026</v>
       </c>
       <c r="B113" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4120,14 +4172,14 @@
         <v>0</v>
       </c>
       <c r="D113" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201028.0)</f>
-        <v>201028</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201027.0)</f>
+        <v>201027</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201028.0)</f>
-        <v>201028</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201027.0)</f>
+        <v>201027</v>
       </c>
       <c r="B114" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4138,14 +4190,14 @@
         <v>0</v>
       </c>
       <c r="D114" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201029.0)</f>
-        <v>201029</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201028.0)</f>
+        <v>201028</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201029.0)</f>
-        <v>201029</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201028.0)</f>
+        <v>201028</v>
       </c>
       <c r="B115" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4156,14 +4208,14 @@
         <v>0</v>
       </c>
       <c r="D115" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201030.0)</f>
-        <v>201030</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201029.0)</f>
+        <v>201029</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201030.0)</f>
-        <v>201030</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201029.0)</f>
+        <v>201029</v>
       </c>
       <c r="B116" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4174,14 +4226,14 @@
         <v>0</v>
       </c>
       <c r="D116" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201031.0)</f>
-        <v>201031</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201030.0)</f>
+        <v>201030</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201031.0)</f>
-        <v>201031</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201030.0)</f>
+        <v>201030</v>
       </c>
       <c r="B117" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4192,14 +4244,14 @@
         <v>0</v>
       </c>
       <c r="D117" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201032.0)</f>
-        <v>201032</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201031.0)</f>
+        <v>201031</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201032.0)</f>
-        <v>201032</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201031.0)</f>
+        <v>201031</v>
       </c>
       <c r="B118" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4210,14 +4262,14 @@
         <v>0</v>
       </c>
       <c r="D118" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201033.0)</f>
-        <v>201033</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201032.0)</f>
+        <v>201032</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201033.0)</f>
-        <v>201033</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201032.0)</f>
+        <v>201032</v>
       </c>
       <c r="B119" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4228,14 +4280,14 @@
         <v>0</v>
       </c>
       <c r="D119" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201034.0)</f>
-        <v>201034</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201033.0)</f>
+        <v>201033</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201034.0)</f>
-        <v>201034</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201033.0)</f>
+        <v>201033</v>
       </c>
       <c r="B120" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
@@ -4246,155 +4298,167 @@
         <v>0</v>
       </c>
       <c r="D120" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201035.0)</f>
-        <v>201035</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201034.0)</f>
+        <v>201034</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201035.0)</f>
-        <v>201035</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201034.0)</f>
+        <v>201034</v>
       </c>
       <c r="B121" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C121" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D121" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201036.0)</f>
-        <v>201036</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201035.0)</f>
+        <v>201035</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201036.0)</f>
-        <v>201036</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201035.0)</f>
+        <v>201035</v>
       </c>
       <c r="B122" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C122" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D122" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
-        <v>201037</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201036.0)</f>
+        <v>201036</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
-        <v>201037</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201036.0)</f>
+        <v>201036</v>
       </c>
       <c r="B123" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C123" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D123" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201038.0)</f>
-        <v>201038</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
+        <v>201037</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201038.0)</f>
-        <v>201038</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
+        <v>201037</v>
       </c>
       <c r="B124" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C124" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D124" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201039.0)</f>
-        <v>201039</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201038.0)</f>
+        <v>201038</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201039.0)</f>
-        <v>201039</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201038.0)</f>
+        <v>201038</v>
       </c>
       <c r="B125" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
-        <v>Event</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C125" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D125" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
-        <v>201040</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201039.0)</f>
+        <v>201039</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
-        <v>201040</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201039.0)</f>
+        <v>201039</v>
       </c>
       <c r="B126" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
-        <v>Bubble, Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Event")</f>
+        <v>Event</v>
       </c>
       <c r="C126" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D126" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201041.0)</f>
-        <v>201041</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
+        <v>201040</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201041.0)</f>
-        <v>201041</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
+        <v>201040</v>
       </c>
       <c r="B127" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
-        <v>Bubble</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble, Camera")</f>
+        <v>Bubble, Camera</v>
       </c>
       <c r="C127" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
       <c r="D127" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
-        <v>201042</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201041.0)</f>
+        <v>201041</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
-        <v>201042</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201041.0)</f>
+        <v>201041</v>
       </c>
       <c r="B128" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
-        <v>End</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Bubble")</f>
+        <v>Bubble</v>
       </c>
       <c r="C128" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D128" s="34"/>
+      <c r="D128" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
+        <v>201042</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="34"/>
-      <c r="B129" s="34"/>
-      <c r="C129" s="34"/>
+      <c r="A129" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
+        <v>201042</v>
+      </c>
+      <c r="B129" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
+        <v>End</v>
+      </c>
+      <c r="C129" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="D129" s="34"/>
     </row>
     <row r="130">
@@ -9718,6 +9782,12 @@
       <c r="B1016" s="34"/>
       <c r="C1016" s="34"/>
       <c r="D1016" s="34"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="34"/>
+      <c r="B1017" s="34"/>
+      <c r="C1017" s="34"/>
+      <c r="D1017" s="34"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9754,7 +9824,7 @@
         <v>Script</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
@@ -9831,8 +9901,8 @@
     </row>
     <row r="6">
       <c r="A6" s="36">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010251.0)</f>
-        <v>1010251</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010261.0)</f>
+        <v>1010261</v>
       </c>
       <c r="B6" s="37"/>
       <c r="C6" s="38"/>
@@ -9843,8 +9913,8 @@
     </row>
     <row r="7">
       <c r="A7" s="36">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010252.0)</f>
-        <v>1010252</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1010262.0)</f>
+        <v>1010262</v>
       </c>
       <c r="B7" s="37"/>
       <c r="C7" s="38"/>
@@ -9855,8 +9925,8 @@
     </row>
     <row r="8">
       <c r="A8" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101033.0)</f>
-        <v>101033</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101034.0)</f>
+        <v>101034</v>
       </c>
       <c r="B8" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"안나")</f>
@@ -9885,8 +9955,8 @@
         <v>Anna_Sigh</v>
       </c>
       <c r="D9" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5} 후 아무리 쫓아와도 그 가위는 안 보이는 것 같네")</f>
-        <v>{fade a=3.5} 후 아무리 쫓아와도 그 가위는 안 보이는 것 같네</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5} 후 그 고양이는 못 찾겠네...")</f>
+        <v>{fade a=3.5} 후 그 고양이는 못 찾겠네...</v>
       </c>
     </row>
     <row r="10">
@@ -10606,7 +10676,7 @@
         <v>Duration</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -10666,7 +10736,7 @@
         <v>-1</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -10706,19 +10776,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101016.0)</f>
         <v>101016</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
+        <v>Cat</v>
+      </c>
       <c r="C7" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
-        <v>ZoomIn</v>
-      </c>
-      <c r="D7" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
-        <v>5.5</v>
-      </c>
-      <c r="E7" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
-        <v>0.3</v>
-      </c>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
+        <v>CameraShift</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
     </row>
     <row r="8">
       <c r="A8" s="34">
@@ -10731,8 +10798,8 @@
         <v>ZoomIn</v>
       </c>
       <c r="D8" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
+        <v>5.5</v>
       </c>
       <c r="E8" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
@@ -10741,56 +10808,56 @@
     </row>
     <row r="9">
       <c r="A9" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101019.0)</f>
-        <v>101019</v>
-      </c>
-      <c r="B9" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101018.0)</f>
+        <v>101018</v>
+      </c>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
+        <v>ZoomIn</v>
+      </c>
+      <c r="D9" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="E9" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101020.0)</f>
+        <v>101020</v>
+      </c>
+      <c r="B10" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
         <v>Anna</v>
       </c>
-      <c r="C9" s="34" t="str">
+      <c r="C10" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
         <v>CameraShift</v>
       </c>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
-        <v>101026</v>
-      </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34" t="str">
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101027.0)</f>
+        <v>101027</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
         <v>ZoomIn</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D11" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
         <v>5.5</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E11" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101028.0)</f>
-        <v>101028</v>
-      </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
-        <v>ZoomOut</v>
-      </c>
-      <c r="D11" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
-      </c>
-      <c r="E11" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -10798,55 +10865,55 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101029.0)</f>
         <v>101029</v>
       </c>
-      <c r="B12" s="34" t="str">
+      <c r="B12" s="34"/>
+      <c r="C12" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
+        <v>ZoomOut</v>
+      </c>
+      <c r="D12" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="E12" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101030.0)</f>
+        <v>101030</v>
+      </c>
+      <c r="B13" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
         <v>Cat</v>
       </c>
-      <c r="C12" s="34" t="str">
+      <c r="C13" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
         <v>ZoomIn</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D13" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.5)</f>
         <v>5.5</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E13" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101034.0)</f>
-        <v>101034</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34" t="str">
+    <row r="14">
+      <c r="A14" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101035.0)</f>
+        <v>101035</v>
+      </c>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
         <v>ZoomOut</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D14" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
-      </c>
-      <c r="E13" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102001.0)</f>
-        <v>102001</v>
-      </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
-        <v>ZoomIn</v>
-      </c>
-      <c r="D14" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
       </c>
       <c r="E14" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
@@ -10855,28 +10922,31 @@
     </row>
     <row r="15">
       <c r="A15" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102001.0)</f>
+        <v>102001</v>
+      </c>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
+        <v>ZoomIn</v>
+      </c>
+      <c r="D15" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="E15" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102002.0)</f>
         <v>102002</v>
       </c>
-      <c r="B15" s="34" t="str">
+      <c r="B16" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
         <v>Cat</v>
-      </c>
-      <c r="C15" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
-        <v>CameraShift</v>
-      </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102004.0)</f>
-        <v>102004</v>
-      </c>
-      <c r="B16" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
-        <v>Anna</v>
       </c>
       <c r="C16" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
@@ -10887,36 +10957,33 @@
     </row>
     <row r="17">
       <c r="A17" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102004.0)</f>
+        <v>102004</v>
+      </c>
+      <c r="B17" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
+        <v>Anna</v>
+      </c>
+      <c r="C17" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
+        <v>CameraShift</v>
+      </c>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102005.0)</f>
         <v>102005</v>
       </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34" t="str">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
         <v>ZoomOut</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D18" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
-      </c>
-      <c r="E17" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103002.0)</f>
-        <v>103002</v>
-      </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
-        <v>ZoomIn</v>
-      </c>
-      <c r="D18" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
       </c>
       <c r="E18" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
@@ -10925,17 +10992,17 @@
     </row>
     <row r="19">
       <c r="A19" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103005.0)</f>
-        <v>103005</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103002.0)</f>
+        <v>103002</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
-        <v>ZoomOut</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
+        <v>ZoomIn</v>
       </c>
       <c r="D19" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
       </c>
       <c r="E19" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
@@ -10944,17 +11011,17 @@
     </row>
     <row r="20">
       <c r="A20" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103015.0)</f>
-        <v>103015</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103005.0)</f>
+        <v>103005</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
-        <v>ZoomIn</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
+        <v>ZoomOut</v>
       </c>
       <c r="D20" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
       </c>
       <c r="E20" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
@@ -10963,120 +11030,123 @@
     </row>
     <row r="21">
       <c r="A21" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103015.0)</f>
+        <v>103015</v>
+      </c>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
+        <v>ZoomIn</v>
+      </c>
+      <c r="D21" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="E21" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103023.0)</f>
         <v>103023</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34" t="str">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shake")</f>
         <v>Shake</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D22" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
         <v>0.1</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E22" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="34">
+    <row r="23">
+      <c r="A23" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103024.0)</f>
         <v>103024</v>
       </c>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34" t="str">
+      <c r="B23" s="34"/>
+      <c r="C23" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
         <v>ZoomOut</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D23" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),8.0)</f>
         <v>8</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E23" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="34">
+    <row r="24">
+      <c r="A24" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104001.0)</f>
         <v>104001</v>
       </c>
-      <c r="B23" s="34" t="str">
+      <c r="B24" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Obstacle_H")</f>
         <v>Obstacle_H</v>
       </c>
-      <c r="C23" s="34" t="str">
+      <c r="C24" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
         <v>CameraShift</v>
       </c>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="34">
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104002.0)</f>
         <v>104002</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34" t="str">
+      <c r="B25" s="34"/>
+      <c r="C25" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
         <v>ZoomIn</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D25" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
         <v>6</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E25" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="34">
+    <row r="26">
+      <c r="A26" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104005.0)</f>
         <v>104005</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34" t="str">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shake")</f>
         <v>Shake</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D26" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
         <v>0.1</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E26" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="34">
+    <row r="27">
+      <c r="A27" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104006.0)</f>
         <v>104006</v>
       </c>
-      <c r="B26" s="34" t="str">
+      <c r="B27" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
         <v>Anna</v>
-      </c>
-      <c r="C26" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
-        <v>CameraShift</v>
-      </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104007.0)</f>
-        <v>104007</v>
-      </c>
-      <c r="B27" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Obstacle_H")</f>
-        <v>Obstacle_H</v>
       </c>
       <c r="C27" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
@@ -11087,12 +11157,12 @@
     </row>
     <row r="28">
       <c r="A28" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
-        <v>104011</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104007.0)</f>
+        <v>104007</v>
       </c>
       <c r="B28" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
-        <v>Anna</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Obstacle_H")</f>
+        <v>Obstacle_H</v>
       </c>
       <c r="C28" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
@@ -11103,46 +11173,43 @@
     </row>
     <row r="29">
       <c r="A29" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),104011.0)</f>
+        <v>104011</v>
+      </c>
+      <c r="B29" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
+        <v>Anna</v>
+      </c>
+      <c r="C29" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
+        <v>CameraShift</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201003.0)</f>
         <v>201003</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34" t="str">
+      <c r="B30" s="34"/>
+      <c r="C30" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shake")</f>
         <v>Shake</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D30" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.05)</f>
         <v>0.05</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E30" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="34">
+    <row r="31">
+      <c r="A31" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201007.0)</f>
         <v>201007</v>
-      </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
-        <v>ZoomIn</v>
-      </c>
-      <c r="D30" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.5)</f>
-        <v>6.5</v>
-      </c>
-      <c r="E30" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201008.0)</f>
-        <v>201008</v>
       </c>
       <c r="B31" s="34"/>
       <c r="C31" s="34" t="str">
@@ -11150,8 +11217,8 @@
         <v>ZoomIn</v>
       </c>
       <c r="D31" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
-        <v>6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.5)</f>
+        <v>6.5</v>
       </c>
       <c r="E31" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
@@ -11160,56 +11227,65 @@
     </row>
     <row r="32">
       <c r="A32" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201008.0)</f>
+        <v>201008</v>
+      </c>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
+        <v>ZoomIn</v>
+      </c>
+      <c r="D32" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="E32" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201009.0)</f>
         <v>201009</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34" t="str">
+      <c r="B33" s="34"/>
+      <c r="C33" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shake")</f>
         <v>Shake</v>
       </c>
-      <c r="D32" s="34">
+      <c r="D33" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.05)</f>
         <v>0.05</v>
       </c>
-      <c r="E32" s="34">
+      <c r="E33" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="34">
+    <row r="34">
+      <c r="A34" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201010.0)</f>
         <v>201010</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34" t="str">
+      <c r="B34" s="34"/>
+      <c r="C34" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomOut")</f>
         <v>ZoomOut</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D34" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
         <v>7</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E34" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
         <v>0.8</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="34">
+    <row r="35">
+      <c r="A35" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201016.0)</f>
         <v>201016</v>
-      </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
-        <v>201037</v>
       </c>
       <c r="B35" s="34"/>
       <c r="C35" s="34"/>
@@ -11218,22 +11294,32 @@
     </row>
     <row r="36">
       <c r="A36" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
+        <v>201037</v>
+      </c>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
         <v>201040</v>
       </c>
-      <c r="B36" s="34" t="str">
+      <c r="B37" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeonong")</f>
         <v>Yeonong</v>
       </c>
-      <c r="C36" s="34" t="str">
+      <c r="C37" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
         <v>ZoomIn</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D37" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
         <v>6</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E37" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -11346,8 +11432,8 @@
     </row>
     <row r="6">
       <c r="A6" s="45">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101018.0)</f>
-        <v>101018</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101019.0)</f>
+        <v>101019</v>
       </c>
       <c r="B6" s="45" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
@@ -11364,8 +11450,8 @@
     </row>
     <row r="7">
       <c r="A7" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101020.0)</f>
-        <v>101020</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101021.0)</f>
+        <v>101021</v>
       </c>
       <c r="B7" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
@@ -11382,8 +11468,8 @@
     </row>
     <row r="8">
       <c r="A8" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101022.0)</f>
-        <v>101022</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101023.0)</f>
+        <v>101023</v>
       </c>
       <c r="B8" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
@@ -11400,8 +11486,8 @@
     </row>
     <row r="9">
       <c r="A9" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101023.0)</f>
-        <v>101023</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101024.0)</f>
+        <v>101024</v>
       </c>
       <c r="B9" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
@@ -11418,8 +11504,8 @@
     </row>
     <row r="10">
       <c r="A10" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101024.0)</f>
-        <v>101024</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101025.0)</f>
+        <v>101025</v>
       </c>
       <c r="B10" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
@@ -11436,8 +11522,8 @@
     </row>
     <row r="11">
       <c r="A11" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
-        <v>101026</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101027.0)</f>
+        <v>101027</v>
       </c>
       <c r="B11" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
@@ -11454,8 +11540,8 @@
     </row>
     <row r="12">
       <c r="A12" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101027.0)</f>
-        <v>101027</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101028.0)</f>
+        <v>101028</v>
       </c>
       <c r="B12" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
@@ -11472,8 +11558,8 @@
     </row>
     <row r="13">
       <c r="A13" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101029.0)</f>
-        <v>101029</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101030.0)</f>
+        <v>101030</v>
       </c>
       <c r="B13" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
@@ -11494,30 +11580,30 @@
         <v>101031</v>
       </c>
       <c r="B14" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat")</f>
+        <v>Cat</v>
+      </c>
+      <c r="C14" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cat_Knockback")</f>
+        <v>Cat_Knockback</v>
+      </c>
+      <c r="D14" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Left")</f>
+        <v>Left</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101032.0)</f>
+        <v>101032</v>
+      </c>
+      <c r="B15" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
         <v>Anna</v>
       </c>
-      <c r="C14" s="34" t="str">
+      <c r="C15" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna_Fall_Start")</f>
         <v>Anna_Fall_Start</v>
-      </c>
-      <c r="D14" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
-        <v>Right</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103008.0)</f>
-        <v>103008</v>
-      </c>
-      <c r="B15" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BigTree")</f>
-        <v>BigTree</v>
-      </c>
-      <c r="C15" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BigTree_Shaked")</f>
-        <v>BigTree_Shaked</v>
       </c>
       <c r="D15" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
@@ -11526,16 +11612,16 @@
     </row>
     <row r="16">
       <c r="A16" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103009.0)</f>
-        <v>103009</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103008.0)</f>
+        <v>103008</v>
       </c>
       <c r="B16" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Scroll")</f>
-        <v>Scroll</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BigTree")</f>
+        <v>BigTree</v>
       </c>
       <c r="C16" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Scroll_Drop")</f>
-        <v>Scroll_Drop</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BigTree_Shaked")</f>
+        <v>BigTree_Shaked</v>
       </c>
       <c r="D16" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
@@ -11544,16 +11630,16 @@
     </row>
     <row r="17">
       <c r="A17" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103016.0)</f>
-        <v>103016</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103009.0)</f>
+        <v>103009</v>
       </c>
       <c r="B17" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ChaseGhost")</f>
-        <v>ChaseGhost</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Scroll")</f>
+        <v>Scroll</v>
       </c>
       <c r="C17" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ChaseGhost_Start")</f>
-        <v>ChaseGhost_Start</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Scroll_Drop")</f>
+        <v>Scroll_Drop</v>
       </c>
       <c r="D17" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
@@ -11562,18 +11648,36 @@
     </row>
     <row r="18">
       <c r="A18" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103016.0)</f>
+        <v>103016</v>
+      </c>
+      <c r="B18" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ChaseGhost")</f>
+        <v>ChaseGhost</v>
+      </c>
+      <c r="C18" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ChaseGhost_Start")</f>
+        <v>ChaseGhost_Start</v>
+      </c>
+      <c r="D18" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
+        <v>Right</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103017.0)</f>
         <v>103017</v>
       </c>
-      <c r="B18" s="34" t="str">
+      <c r="B19" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
         <v>Anna</v>
       </c>
-      <c r="C18" s="34" t="str">
+      <c r="C19" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna_Surprised")</f>
         <v>Anna_Surprised</v>
       </c>
-      <c r="D18" s="34" t="str">
+      <c r="D19" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Left")</f>
         <v>Left</v>
       </c>
@@ -11706,8 +11810,8 @@
     </row>
     <row r="7">
       <c r="A7" s="47">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101019.0)</f>
-        <v>101019</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101020.0)</f>
+        <v>101020</v>
       </c>
       <c r="B7" s="45" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
@@ -12003,8 +12107,8 @@
     </row>
     <row r="2">
       <c r="A2" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101025.0)</f>
-        <v>101025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101026.0)</f>
+        <v>101026</v>
       </c>
       <c r="B2" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"어떻게 할까?")</f>
@@ -12073,10 +12177,47 @@
     </row>
     <row r="2">
       <c r="A2" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101017.0)</f>
+        <v>101017</v>
+      </c>
+      <c r="B2" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101028.0)</f>
+        <v>101028</v>
+      </c>
+      <c r="B3" s="34"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),101032.0)</f>
+        <v>101032</v>
+      </c>
+      <c r="B4" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102002.0)</f>
+        <v>102002</v>
+      </c>
+      <c r="B5" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),103017.0)</f>
         <v>103017</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B6" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
         <v>0.5</v>
       </c>
@@ -12109,52 +12250,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" s="50" t="s">
         <v>52</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E1" s="51" t="s">
         <v>61</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H1" s="39" t="s">
         <v>62</v>
       </c>
       <c r="I1" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="39" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="39" t="s">
         <v>93</v>
-      </c>
-      <c r="J1" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="39" t="s">
-        <v>90</v>
       </c>
       <c r="L1" s="44" t="s">
         <v>62</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O1" s="46" t="s">
         <v>62</v>
       </c>
       <c r="P1" s="46" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q1" s="52" t="s">
         <v>62</v>
@@ -12163,7 +12304,7 @@
         <v>63</v>
       </c>
       <c r="S1" s="53" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -12184,10 +12325,10 @@
         <v>21</v>
       </c>
       <c r="M2" s="55" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N2" s="55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -12208,10 +12349,10 @@
         <v>21</v>
       </c>
       <c r="M3" s="55" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N3" s="55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -12219,7 +12360,7 @@
         <v>101003.0</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>52</v>
@@ -12231,10 +12372,10 @@
         <v>101004.0</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
@@ -12242,7 +12383,7 @@
         <v>101004.0</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>52</v>
@@ -12254,10 +12395,10 @@
         <v>101005.0</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
@@ -12278,10 +12419,10 @@
         <v>21</v>
       </c>
       <c r="M6" s="55" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N6" s="55" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -12302,10 +12443,10 @@
         <v>21</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N7" s="55" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -12313,7 +12454,7 @@
         <v>101007.0</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -12325,10 +12466,10 @@
         <v>101008.0</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9">
@@ -12336,7 +12477,7 @@
         <v>101008.0</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>52</v>
@@ -12348,10 +12489,10 @@
         <v>101009.0</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -12359,10 +12500,10 @@
         <v>101009.0</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D10" s="6">
         <v>0.0</v>
@@ -12374,7 +12515,7 @@
       <c r="G10" s="57"/>
       <c r="H10" s="60"/>
       <c r="I10" s="61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J10" s="60">
         <v>7.0</v>
@@ -12386,7 +12527,7 @@
         <v>21</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="37"/>
       <c r="R10" s="37"/>
@@ -12396,10 +12537,10 @@
         <v>101010.0</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" s="6">
         <v>0.0</v>
@@ -12411,7 +12552,7 @@
       <c r="G11" s="57"/>
       <c r="H11" s="60"/>
       <c r="I11" s="61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J11" s="60">
         <v>6.0</v>
@@ -12423,7 +12564,7 @@
         <v>21</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q11" s="37"/>
       <c r="R11" s="37"/>
@@ -12433,10 +12574,10 @@
         <v>101011.0</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D12" s="6">
         <v>2.0</v>
@@ -12448,7 +12589,7 @@
       <c r="G12" s="57"/>
       <c r="H12" s="60"/>
       <c r="I12" s="61" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J12" s="60">
         <v>0.05</v>
@@ -12460,7 +12601,7 @@
         <v>21</v>
       </c>
       <c r="P12" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q12" s="37"/>
       <c r="R12" s="37"/>
@@ -12470,7 +12611,7 @@
         <v>101012.0</v>
       </c>
       <c r="B13" s="59" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>32</v>
@@ -12484,10 +12625,10 @@
       <c r="F13" s="6"/>
       <c r="G13" s="57"/>
       <c r="H13" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J13" s="60"/>
       <c r="K13" s="60"/>
@@ -12501,7 +12642,7 @@
         <v>101013.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>40</v>
@@ -12526,10 +12667,10 @@
         <v>101014.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D15" s="6">
         <v>0.0</v>
@@ -12543,7 +12684,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="63" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="J15" s="60"/>
       <c r="K15" s="60"/>
@@ -12551,7 +12692,7 @@
         <v>21</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q15" s="37"/>
       <c r="R15" s="37"/>
@@ -12561,7 +12702,7 @@
         <v>101015.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>55</v>
@@ -12582,7 +12723,7 @@
         <v>21</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Q16" s="37"/>
       <c r="R16" s="37"/>
@@ -12591,59 +12732,55 @@
       <c r="A17" s="6">
         <v>101016.0</v>
       </c>
-      <c r="B17" s="59" t="s">
-        <v>120</v>
+      <c r="B17" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="6">
-        <v>1.0</v>
-      </c>
+      <c r="D17" s="6"/>
       <c r="E17" s="6">
         <v>101017.0</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="57"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J17" s="60">
-        <v>5.5</v>
-      </c>
-      <c r="K17" s="60">
-        <v>0.3</v>
-      </c>
+      <c r="H17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
       <c r="O17" s="38"/>
       <c r="P17" s="37"/>
       <c r="Q17" s="37"/>
       <c r="R17" s="37"/>
     </row>
     <row r="18">
-      <c r="A18" s="6">
+      <c r="A18" s="64">
         <v>101017.0</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="D18" s="6">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E18" s="6">
         <v>101018.0</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="57"/>
-      <c r="H18" s="60"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="61" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J18" s="60">
-        <v>5.0</v>
+        <v>5.5</v>
       </c>
       <c r="K18" s="60">
         <v>0.3</v>
@@ -12652,699 +12789,724 @@
       <c r="P18" s="37"/>
       <c r="Q18" s="37"/>
       <c r="R18" s="37"/>
+      <c r="S18" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6">
         <v>101018.0</v>
       </c>
-      <c r="B19" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="65">
-        <v>0.0</v>
+      <c r="B19" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2.0</v>
       </c>
       <c r="E19" s="6">
         <v>101019.0</v>
       </c>
-      <c r="F19" s="65"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="M19" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="N19" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O19" s="67"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="K19" s="60">
+        <v>0.3</v>
+      </c>
+      <c r="O19" s="38"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="37"/>
     </row>
     <row r="20">
       <c r="A20" s="6">
         <v>101019.0</v>
       </c>
-      <c r="B20" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="65">
+      <c r="B20" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="67">
         <v>0.0</v>
       </c>
       <c r="E20" s="6">
         <v>101020.0</v>
       </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="66"/>
-      <c r="H20" s="62" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>116</v>
-      </c>
+      <c r="F20" s="67"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="63"/>
       <c r="J20" s="62"/>
       <c r="K20" s="62"/>
-      <c r="O20" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" s="68" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
+      <c r="L20" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="M20" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="N20" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="O20" s="69"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
     </row>
     <row r="21">
       <c r="A21" s="6">
         <v>101020.0</v>
       </c>
-      <c r="B21" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="65">
+      <c r="B21" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" s="66" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="67">
         <v>0.0</v>
       </c>
       <c r="E21" s="6">
         <v>101021.0</v>
       </c>
-      <c r="F21" s="65"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="63"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="63" t="s">
+        <v>119</v>
+      </c>
       <c r="J21" s="62"/>
       <c r="K21" s="62"/>
-      <c r="L21" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="M21" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="N21" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O21" s="67"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
+      <c r="O21" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
     </row>
     <row r="22">
       <c r="A22" s="6">
         <v>101021.0</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="65">
+        <v>131</v>
+      </c>
+      <c r="C22" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="67">
         <v>0.0</v>
       </c>
       <c r="E22" s="6">
         <v>101022.0</v>
       </c>
-      <c r="F22" s="65"/>
-      <c r="G22" s="66"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="68"/>
       <c r="H22" s="62"/>
       <c r="I22" s="63"/>
       <c r="J22" s="62"/>
       <c r="K22" s="62"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="68"/>
-      <c r="R22" s="68"/>
+      <c r="L22" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="M22" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="N22" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="O22" s="69"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
     </row>
     <row r="23">
       <c r="A23" s="6">
         <v>101022.0</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="65">
+        <v>133</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="67">
         <v>0.0</v>
       </c>
       <c r="E23" s="6">
         <v>101023.0</v>
       </c>
-      <c r="F23" s="65"/>
-      <c r="G23" s="66"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="68"/>
       <c r="H23" s="62"/>
       <c r="I23" s="63"/>
       <c r="J23" s="62"/>
       <c r="K23" s="62"/>
-      <c r="L23" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="M23" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="N23" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
     </row>
     <row r="24">
       <c r="A24" s="6">
         <v>101023.0</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="65">
+      <c r="D24" s="67">
         <v>0.0</v>
       </c>
       <c r="E24" s="6">
         <v>101024.0</v>
       </c>
-      <c r="F24" s="65"/>
-      <c r="G24" s="66"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="68"/>
       <c r="H24" s="62"/>
       <c r="I24" s="63"/>
       <c r="J24" s="62"/>
       <c r="K24" s="62"/>
       <c r="L24" s="34" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O24" s="67"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
+        <v>108</v>
+      </c>
+      <c r="O24" s="69"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
     </row>
     <row r="25">
       <c r="A25" s="6">
         <v>101024.0</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="65">
-        <v>1.0</v>
+      <c r="D25" s="67">
+        <v>0.0</v>
       </c>
       <c r="E25" s="6">
         <v>101025.0</v>
       </c>
-      <c r="F25" s="65"/>
-      <c r="G25" s="66"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="68"/>
       <c r="H25" s="62"/>
       <c r="I25" s="63"/>
       <c r="J25" s="62"/>
       <c r="K25" s="62"/>
       <c r="L25" s="34" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="M25" s="34" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="O25" s="67"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
+        <v>108</v>
+      </c>
+      <c r="O25" s="69"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="70"/>
+      <c r="R25" s="70"/>
     </row>
     <row r="26">
       <c r="A26" s="6">
         <v>101025.0</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="65">
-        <v>0.0</v>
-      </c>
-      <c r="E26" s="65">
-        <v>0.0</v>
-      </c>
-      <c r="F26" s="65"/>
-      <c r="G26" s="66"/>
+        <v>138</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="67">
+        <v>1.0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>101026.0</v>
+      </c>
+      <c r="F26" s="67"/>
+      <c r="G26" s="68"/>
       <c r="H26" s="62"/>
       <c r="I26" s="63"/>
       <c r="J26" s="62"/>
       <c r="K26" s="62"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="68"/>
-      <c r="Q26" s="68" t="s">
+      <c r="L26" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="R26" s="37">
-        <v>2.0</v>
-      </c>
+      <c r="M26" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="N26" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="O26" s="69"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="70"/>
+      <c r="R26" s="70"/>
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <v>1010251.0</v>
+        <v>101026.0</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>135</v>
-      </c>
-      <c r="C27" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="65">
+        <v>65</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="67">
         <v>0.0</v>
       </c>
-      <c r="E27" s="6">
-        <v>101026.0</v>
-      </c>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
+      <c r="E27" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="F27" s="67"/>
+      <c r="G27" s="68"/>
       <c r="H27" s="62"/>
       <c r="I27" s="63"/>
       <c r="J27" s="62"/>
       <c r="K27" s="62"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="68"/>
-      <c r="Q27" s="68"/>
-      <c r="R27" s="68"/>
+      <c r="O27" s="69"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="70" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" s="37">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6">
-        <v>1010252.0</v>
+        <v>1010261.0</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="65">
+      <c r="D28" s="67">
         <v>0.0</v>
       </c>
       <c r="E28" s="6">
-        <v>101029.0</v>
-      </c>
-      <c r="F28" s="65"/>
-      <c r="G28" s="66"/>
+        <v>101027.0</v>
+      </c>
+      <c r="F28" s="67"/>
+      <c r="G28" s="68"/>
       <c r="H28" s="62"/>
       <c r="I28" s="63"/>
       <c r="J28" s="62"/>
       <c r="K28" s="62"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="68"/>
-      <c r="Q28" s="68"/>
-      <c r="R28" s="68"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="70"/>
+      <c r="R28" s="70"/>
     </row>
     <row r="29">
       <c r="A29" s="6">
-        <v>101026.0</v>
+        <v>1010262.0</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="65">
+        <v>141</v>
+      </c>
+      <c r="C29" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="67">
         <v>0.0</v>
       </c>
       <c r="E29" s="6">
-        <v>1010267.0</v>
-      </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66"/>
+        <v>101030.0</v>
+      </c>
+      <c r="F29" s="67"/>
+      <c r="G29" s="68"/>
       <c r="H29" s="62"/>
-      <c r="I29" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="J29" s="62">
-        <v>5.5</v>
-      </c>
-      <c r="K29" s="62">
-        <v>3.0</v>
-      </c>
-      <c r="L29" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="N29" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="O29" s="67"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="68"/>
-      <c r="R29" s="68"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
+      <c r="R29" s="70"/>
     </row>
     <row r="30">
       <c r="A30" s="6">
         <v>101027.0</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="65">
+        <v>142</v>
+      </c>
+      <c r="C30" s="66" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="67">
         <v>0.0</v>
       </c>
       <c r="E30" s="6">
         <v>101028.0</v>
       </c>
-      <c r="F30" s="65"/>
-      <c r="G30" s="66"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="68"/>
       <c r="H30" s="62"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
+      <c r="I30" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30" s="62">
+        <v>5.5</v>
+      </c>
+      <c r="K30" s="62">
+        <v>3.0</v>
+      </c>
       <c r="L30" s="34" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O30" s="67"/>
-      <c r="P30" s="68"/>
-      <c r="Q30" s="68"/>
-      <c r="R30" s="68"/>
+        <v>102</v>
+      </c>
+      <c r="O30" s="69"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="70"/>
     </row>
     <row r="31">
-      <c r="A31" s="6">
+      <c r="A31" s="71">
         <v>101028.0</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="65">
+        <v>145</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="67">
         <v>0.0</v>
       </c>
       <c r="E31" s="6">
-        <v>101025.0</v>
-      </c>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66"/>
+        <v>101029.0</v>
+      </c>
+      <c r="F31" s="67"/>
+      <c r="G31" s="68"/>
       <c r="H31" s="62"/>
-      <c r="I31" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="J31" s="62">
-        <v>6.0</v>
-      </c>
-      <c r="K31" s="62">
-        <v>0.8</v>
-      </c>
-      <c r="O31" s="67"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="68"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="M31" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="N31" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="O31" s="69"/>
+      <c r="P31" s="70"/>
+      <c r="Q31" s="70"/>
+      <c r="R31" s="70"/>
     </row>
     <row r="32">
       <c r="A32" s="6">
         <v>101029.0</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>144</v>
-      </c>
-      <c r="C32" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="D32" s="65">
-        <v>2.0</v>
+        <v>148</v>
+      </c>
+      <c r="C32" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="67">
+        <v>0.0</v>
       </c>
       <c r="E32" s="6">
-        <v>101030.0</v>
-      </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="62" t="s">
-        <v>115</v>
-      </c>
+        <v>101026.0</v>
+      </c>
+      <c r="F32" s="67"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="62"/>
       <c r="I32" s="63" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="J32" s="62">
-        <v>5.5</v>
+        <v>6.0</v>
       </c>
       <c r="K32" s="62">
-        <v>2.0</v>
-      </c>
-      <c r="L32" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="M32" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="N32" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="O32" s="67"/>
-      <c r="P32" s="68"/>
-      <c r="Q32" s="68"/>
-      <c r="R32" s="68"/>
+        <v>0.8</v>
+      </c>
+      <c r="O32" s="69"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="70"/>
+      <c r="R32" s="70"/>
     </row>
     <row r="33">
       <c r="A33" s="6">
         <v>101030.0</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="65">
-        <v>0.0</v>
+        <v>150</v>
+      </c>
+      <c r="C33" s="66" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="67">
+        <v>2.0</v>
       </c>
       <c r="E33" s="6">
         <v>101031.0</v>
       </c>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="62"/>
-      <c r="I33" s="63"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="68"/>
-      <c r="Q33" s="68"/>
-      <c r="R33" s="68"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="I33" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="J33" s="62">
+        <v>5.5</v>
+      </c>
+      <c r="K33" s="62">
+        <v>2.0</v>
+      </c>
+      <c r="L33" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="M33" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="N33" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="O33" s="69"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="70"/>
+      <c r="R33" s="70"/>
     </row>
     <row r="34">
-      <c r="A34" s="6">
+      <c r="A34" s="71">
         <v>101031.0</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="65">
+      <c r="D34" s="67">
         <v>0.0</v>
       </c>
       <c r="E34" s="6">
         <v>101032.0</v>
       </c>
-      <c r="F34" s="65"/>
-      <c r="G34" s="66"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="68"/>
       <c r="H34" s="62"/>
       <c r="I34" s="63"/>
       <c r="J34" s="62"/>
       <c r="K34" s="62"/>
-      <c r="L34" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="N34" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="O34" s="67"/>
-      <c r="P34" s="68"/>
-      <c r="Q34" s="68"/>
-      <c r="R34" s="68"/>
+      <c r="L34" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="O34" s="69"/>
+      <c r="P34" s="70"/>
+      <c r="Q34" s="70"/>
+      <c r="R34" s="70"/>
     </row>
     <row r="35">
-      <c r="A35" s="69">
+      <c r="A35" s="71">
         <v>101032.0</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="D35" s="65">
+        <v>154</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="67">
         <v>0.0</v>
       </c>
       <c r="E35" s="6">
         <v>101033.0</v>
       </c>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="68"/>
       <c r="H35" s="62"/>
       <c r="I35" s="63"/>
       <c r="J35" s="62"/>
       <c r="K35" s="62"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="68"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="68"/>
+      <c r="L35" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="N35" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="O35" s="69"/>
+      <c r="P35" s="70"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="70"/>
+      <c r="S35" s="4">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6">
+      <c r="A36" s="72">
         <v>101033.0</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="C36" s="64" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="65">
+        <v>156</v>
+      </c>
+      <c r="C36" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="67">
         <v>0.0</v>
       </c>
       <c r="E36" s="6">
         <v>101034.0</v>
       </c>
-      <c r="F36" s="65" t="s">
-        <v>101</v>
-      </c>
-      <c r="G36" s="66" t="s">
-        <v>151</v>
-      </c>
+      <c r="F36" s="67"/>
+      <c r="G36" s="68"/>
       <c r="H36" s="62"/>
       <c r="I36" s="63"/>
       <c r="J36" s="62"/>
       <c r="K36" s="62"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
+      <c r="O36" s="69"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
     </row>
     <row r="37">
       <c r="A37" s="6">
         <v>101034.0</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>152</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="65">
+        <v>157</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="67">
         <v>0.0</v>
       </c>
       <c r="E37" s="6">
         <v>101035.0</v>
       </c>
-      <c r="F37" s="65"/>
-      <c r="G37" s="66"/>
+      <c r="F37" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="G37" s="68" t="s">
+        <v>158</v>
+      </c>
       <c r="H37" s="62"/>
-      <c r="I37" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="J37" s="62">
-        <v>8.0</v>
-      </c>
-      <c r="K37" s="62">
-        <v>0.8</v>
-      </c>
-      <c r="O37" s="67"/>
-      <c r="P37" s="68"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="68"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="62"/>
+      <c r="K37" s="62"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="70"/>
     </row>
     <row r="38">
       <c r="A38" s="6">
         <v>101035.0</v>
       </c>
       <c r="B38" s="56" t="s">
-        <v>153</v>
-      </c>
-      <c r="C38" s="64" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="E38" s="6">
+        <v>101036.0</v>
+      </c>
+      <c r="F38" s="67"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" s="62">
+        <v>8.0</v>
+      </c>
+      <c r="K38" s="62">
+        <v>0.8</v>
+      </c>
+      <c r="O38" s="69"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6">
+        <v>101036.0</v>
+      </c>
+      <c r="B39" s="56" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="65">
+      <c r="D39" s="67">
         <v>0.0</v>
       </c>
-      <c r="E38" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="F38" s="65"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="70">
+      <c r="E39" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="F39" s="67"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="62"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="70"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="73">
         <v>102001.0</v>
       </c>
-      <c r="B39" s="71" t="s">
-        <v>155</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J39" s="60">
-        <v>6.0</v>
-      </c>
-      <c r="K39" s="60">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="70">
-        <v>102002.0</v>
-      </c>
-      <c r="B40" s="71" t="s">
-        <v>156</v>
+      <c r="B40" s="74" t="s">
+        <v>162</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>32</v>
@@ -13352,53 +13514,59 @@
       <c r="D40" s="6">
         <v>0.0</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>116</v>
+      <c r="I40" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J40" s="60">
+        <v>6.0</v>
+      </c>
+      <c r="K40" s="60">
+        <v>0.8</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="70">
-        <v>102003.0</v>
-      </c>
-      <c r="B41" s="71" t="s">
-        <v>157</v>
+      <c r="A41" s="75">
+        <v>102002.0</v>
+      </c>
+      <c r="B41" s="74" t="s">
+        <v>163</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="D41" s="6">
         <v>0.0</v>
       </c>
+      <c r="H41" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="S41" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="70">
-        <v>102004.0</v>
-      </c>
-      <c r="B42" s="71" t="s">
-        <v>158</v>
+      <c r="A42" s="73">
+        <v>102003.0</v>
+      </c>
+      <c r="B42" s="74" t="s">
+        <v>164</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D42" s="6">
         <v>0.0</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>116</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="70">
-        <v>102005.0</v>
-      </c>
-      <c r="B43" s="71" t="s">
-        <v>159</v>
+      <c r="A43" s="73">
+        <v>102004.0</v>
+      </c>
+      <c r="B43" s="74" t="s">
+        <v>165</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>32</v>
@@ -13406,106 +13574,103 @@
       <c r="D43" s="6">
         <v>0.0</v>
       </c>
-      <c r="I43" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="J43" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="K43" s="6">
-        <v>0.8</v>
+      <c r="H43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="70">
-        <v>102006.0</v>
-      </c>
-      <c r="B44" s="71" t="s">
-        <v>160</v>
+      <c r="A44" s="73">
+        <v>102005.0</v>
+      </c>
+      <c r="B44" s="74" t="s">
+        <v>166</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D44" s="6">
         <v>0.0</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>154</v>
+      <c r="I44" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="J44" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="K44" s="6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6">
-        <v>103001.0</v>
-      </c>
-      <c r="B45" s="4" t="s">
+      <c r="A45" s="73">
+        <v>102006.0</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="72">
-        <v>1.0</v>
-      </c>
-      <c r="E45" s="6">
-        <v>103002.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6">
+        <v>103001.0</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="76">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="6">
         <v>103002.0</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E46" s="6">
-        <v>103003.0</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="K46" s="6">
-        <v>0.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6">
+        <v>103002.0</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E47" s="6">
         <v>103003.0</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E47" s="6">
-        <v>103004.0</v>
-      </c>
-      <c r="F47" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="G47" s="58" t="s">
-        <v>164</v>
+      <c r="H47" s="6"/>
+      <c r="I47" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J47" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="K47" s="6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6">
-        <v>103004.0</v>
+        <v>103003.0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>52</v>
@@ -13514,69 +13679,71 @@
         <v>0.0</v>
       </c>
       <c r="E48" s="6">
-        <v>103005.0</v>
+        <v>103004.0</v>
       </c>
       <c r="F48" s="57" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G48" s="58" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6">
-        <v>103005.0</v>
+        <v>103004.0</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D49" s="6">
         <v>0.0</v>
       </c>
       <c r="E49" s="6">
-        <v>103006.0</v>
-      </c>
-      <c r="H49" s="6"/>
-      <c r="I49" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="J49" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="K49" s="6">
-        <v>0.8</v>
+        <v>103005.0</v>
+      </c>
+      <c r="F49" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="G49" s="58" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <v>103006.0</v>
+        <v>103005.0</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D50" s="6">
         <v>0.0</v>
       </c>
       <c r="E50" s="6">
-        <v>103007.0</v>
+        <v>103006.0</v>
       </c>
       <c r="H50" s="6"/>
-      <c r="I50" s="61"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
+      <c r="I50" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="J50" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="K50" s="6">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6">
-        <v>103007.0</v>
+        <v>103006.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>40</v>
@@ -13585,84 +13752,88 @@
         <v>0.0</v>
       </c>
       <c r="E51" s="6">
-        <v>103008.0</v>
-      </c>
+        <v>103007.0</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="61"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
     </row>
     <row r="52">
       <c r="A52" s="6">
+        <v>103007.0</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E52" s="6">
         <v>103008.0</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="E52" s="6">
-        <v>103009.0</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N52" s="55" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6">
-        <v>103009.0</v>
+        <v>103008.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D53" s="6">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="E53" s="6">
-        <v>103010.0</v>
+        <v>103009.0</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>99</v>
+        <v>39</v>
+      </c>
+      <c r="N53" s="55" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6">
-        <v>103010.0</v>
+        <v>103009.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D54" s="6">
         <v>0.0</v>
       </c>
       <c r="E54" s="6">
-        <v>103011.0</v>
+        <v>103010.0</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6">
-        <v>103011.0</v>
+        <v>103010.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>40</v>
@@ -13671,15 +13842,15 @@
         <v>0.0</v>
       </c>
       <c r="E55" s="6">
-        <v>103012.0</v>
+        <v>103011.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6">
-        <v>103012.0</v>
+        <v>103011.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>40</v>
@@ -13688,15 +13859,15 @@
         <v>0.0</v>
       </c>
       <c r="E56" s="6">
-        <v>103013.0</v>
+        <v>103012.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6">
-        <v>103013.0</v>
+        <v>103012.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>40</v>
@@ -13705,15 +13876,15 @@
         <v>0.0</v>
       </c>
       <c r="E57" s="6">
-        <v>103014.0</v>
+        <v>103013.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6">
-        <v>103014.0</v>
+        <v>103013.0</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>40</v>
@@ -13722,143 +13893,137 @@
         <v>0.0</v>
       </c>
       <c r="E58" s="6">
-        <v>103015.0</v>
+        <v>103014.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6">
-        <v>103015.0</v>
+        <v>103014.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D59" s="6">
         <v>0.0</v>
       </c>
       <c r="E59" s="6">
-        <v>103016.0</v>
-      </c>
-      <c r="H59" s="6"/>
-      <c r="I59" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J59" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="K59" s="6">
-        <v>0.8</v>
+        <v>103015.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6">
-        <v>103016.0</v>
+        <v>103015.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D60" s="6">
         <v>0.0</v>
       </c>
       <c r="E60" s="6">
-        <v>103017.0</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="N60" s="55" t="s">
-        <v>99</v>
+        <v>103016.0</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J60" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="K60" s="6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6">
+        <v>103016.0</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E61" s="6">
         <v>103017.0</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="L61" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N61" s="55" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="64">
+        <v>103017.0</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D62" s="6">
         <v>2.0</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E62" s="6">
         <v>103018.0</v>
       </c>
-      <c r="L61" s="55" t="s">
+      <c r="L62" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="M61" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="N61" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="S61" s="4">
+      <c r="M62" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N62" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="S62" s="4">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6">
-        <v>103018.0</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E62" s="6">
-        <v>103019.0</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62" s="58" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6">
-        <v>103019.0</v>
+        <v>103018.0</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D63" s="6">
         <v>0.0</v>
       </c>
       <c r="E63" s="6">
-        <v>103020.0</v>
-      </c>
-      <c r="O63" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P63" s="37" t="s">
-        <v>110</v>
+        <v>103019.0</v>
+      </c>
+      <c r="F63" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="G63" s="58" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6">
-        <v>103020.0</v>
+        <v>103019.0</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>55</v>
@@ -13867,22 +14032,21 @@
         <v>0.0</v>
       </c>
       <c r="E64" s="6">
-        <v>103021.0</v>
-      </c>
-      <c r="N64" s="55"/>
+        <v>103020.0</v>
+      </c>
       <c r="O64" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P64" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6">
-        <v>103021.0</v>
+        <v>103020.0</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>55</v>
@@ -13891,7 +14055,7 @@
         <v>0.0</v>
       </c>
       <c r="E65" s="6">
-        <v>103022.0</v>
+        <v>103021.0</v>
       </c>
       <c r="N65" s="55"/>
       <c r="O65" s="4" t="s">
@@ -13903,10 +14067,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6">
-        <v>103022.0</v>
+        <v>103021.0</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>55</v>
@@ -13915,137 +14079,138 @@
         <v>0.0</v>
       </c>
       <c r="E66" s="6">
-        <v>103023.0</v>
+        <v>103022.0</v>
       </c>
       <c r="N66" s="55"/>
       <c r="O66" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P66" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6">
-        <v>103023.0</v>
+        <v>103022.0</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D67" s="6">
         <v>0.0</v>
       </c>
       <c r="E67" s="6">
-        <v>103024.0</v>
-      </c>
-      <c r="H67" s="60"/>
-      <c r="I67" s="61" t="s">
-        <v>112</v>
-      </c>
-      <c r="J67" s="60">
-        <v>0.1</v>
-      </c>
-      <c r="K67" s="60">
-        <v>-1.0</v>
+        <v>103023.0</v>
       </c>
       <c r="N67" s="55"/>
       <c r="O67" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P67" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6">
-        <v>103024.0</v>
+        <v>103023.0</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="D68" s="6">
         <v>0.0</v>
       </c>
       <c r="E68" s="6">
-        <v>103025.0</v>
-      </c>
-      <c r="H68" s="6"/>
+        <v>103024.0</v>
+      </c>
+      <c r="H68" s="60"/>
       <c r="I68" s="61" t="s">
-        <v>143</v>
-      </c>
-      <c r="J68" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="K68" s="6">
-        <v>0.8</v>
+        <v>115</v>
+      </c>
+      <c r="J68" s="60">
+        <v>0.1</v>
+      </c>
+      <c r="K68" s="60">
+        <v>-1.0</v>
+      </c>
+      <c r="N68" s="55"/>
+      <c r="O68" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P68" s="37" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6">
-        <v>103025.0</v>
-      </c>
-      <c r="B69" s="73" t="s">
-        <v>187</v>
+        <v>103024.0</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D69" s="6">
         <v>0.0</v>
       </c>
       <c r="E69" s="6">
-        <v>103026.0</v>
+        <v>103025.0</v>
+      </c>
+      <c r="H69" s="6"/>
+      <c r="I69" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="J69" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="K69" s="6">
+        <v>0.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6">
-        <v>103026.0</v>
+        <v>103025.0</v>
+      </c>
+      <c r="B70" s="77" t="s">
+        <v>193</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D70" s="6">
         <v>0.0</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>154</v>
+      <c r="E70" s="6">
+        <v>103026.0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="70">
-        <v>104001.0</v>
-      </c>
-      <c r="B71" s="71" t="s">
-        <v>188</v>
+      <c r="A71" s="6">
+        <v>103026.0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D71" s="6">
         <v>0.0</v>
       </c>
-      <c r="E71" s="6">
-        <v>104002.0</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>116</v>
+      <c r="E71" s="4" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="70">
-        <v>104002.0</v>
-      </c>
-      <c r="B72" s="71" t="s">
-        <v>162</v>
+      <c r="A72" s="73">
+        <v>104001.0</v>
+      </c>
+      <c r="B72" s="74" t="s">
+        <v>194</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>32</v>
@@ -14054,47 +14219,47 @@
         <v>0.0</v>
       </c>
       <c r="E72" s="6">
-        <v>104003.0</v>
-      </c>
-      <c r="I72" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="J72" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="K72" s="6">
-        <v>0.5</v>
+        <v>104002.0</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="70">
-        <v>104003.0</v>
-      </c>
-      <c r="B73" s="71" t="s">
-        <v>190</v>
+      <c r="A73" s="73">
+        <v>104002.0</v>
+      </c>
+      <c r="B73" s="74" t="s">
+        <v>169</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D73" s="6">
         <v>0.0</v>
       </c>
       <c r="E73" s="6">
-        <v>104004.0</v>
-      </c>
-      <c r="O73" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="P73" s="37" t="s">
-        <v>113</v>
+        <v>104003.0</v>
+      </c>
+      <c r="I73" s="61" t="s">
+        <v>112</v>
+      </c>
+      <c r="J73" s="6">
+        <v>6.0</v>
+      </c>
+      <c r="K73" s="6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="70">
-        <v>104004.0</v>
-      </c>
-      <c r="B74" s="71" t="s">
-        <v>191</v>
+      <c r="A74" s="73">
+        <v>104003.0</v>
+      </c>
+      <c r="B74" s="74" t="s">
+        <v>196</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>55</v>
@@ -14103,103 +14268,109 @@
         <v>0.0</v>
       </c>
       <c r="E74" s="6">
-        <v>104005.0</v>
+        <v>104004.0</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P74" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="70">
-        <v>104005.0</v>
-      </c>
-      <c r="B75" s="71" t="s">
-        <v>192</v>
+      <c r="A75" s="73">
+        <v>104004.0</v>
+      </c>
+      <c r="B75" s="74" t="s">
+        <v>197</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D75" s="6">
         <v>0.0</v>
       </c>
       <c r="E75" s="6">
-        <v>104006.0</v>
-      </c>
-      <c r="I75" s="61" t="s">
-        <v>112</v>
-      </c>
-      <c r="J75" s="60">
-        <v>0.1</v>
-      </c>
-      <c r="K75" s="60">
-        <v>-1.0</v>
+        <v>104005.0</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P75" s="37" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="70">
-        <v>104006.0</v>
-      </c>
-      <c r="B76" s="71" t="s">
-        <v>65</v>
+      <c r="A76" s="73">
+        <v>104005.0</v>
+      </c>
+      <c r="B76" s="74" t="s">
+        <v>198</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="D76" s="6">
         <v>0.0</v>
       </c>
       <c r="E76" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76" s="4" t="s">
+        <v>104006.0</v>
+      </c>
+      <c r="I76" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="J76" s="60">
+        <v>0.1</v>
+      </c>
+      <c r="K76" s="60">
+        <v>-1.0</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="P76" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="J76" s="60"/>
-      <c r="K76" s="60"/>
-      <c r="Q76" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="R76" s="4">
-        <v>2.0</v>
-      </c>
     </row>
     <row r="77">
-      <c r="A77" s="70">
-        <v>1040061.0</v>
-      </c>
-      <c r="B77" s="71" t="s">
-        <v>194</v>
-      </c>
-      <c r="C77" s="64" t="s">
-        <v>52</v>
+      <c r="A77" s="73">
+        <v>104006.0</v>
+      </c>
+      <c r="B77" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="D77" s="6">
         <v>0.0</v>
       </c>
       <c r="E77" s="6">
-        <v>104007.0</v>
+        <v>0.0</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J77" s="60"/>
+      <c r="K77" s="60"/>
+      <c r="Q77" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="R77" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="70">
-        <v>1040062.0</v>
-      </c>
-      <c r="B78" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="C78" s="64" t="s">
+      <c r="A78" s="73">
+        <v>1040061.0</v>
+      </c>
+      <c r="B78" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="C78" s="66" t="s">
         <v>52</v>
       </c>
       <c r="D78" s="6">
@@ -14210,166 +14381,157 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="70">
-        <v>104007.0</v>
-      </c>
-      <c r="B79" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>108</v>
+      <c r="A79" s="73">
+        <v>1040062.0</v>
+      </c>
+      <c r="B79" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79" s="66" t="s">
+        <v>52</v>
       </c>
       <c r="D79" s="6">
         <v>0.0</v>
       </c>
       <c r="E79" s="6">
-        <v>104008.0</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="O79" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="P79" s="37" t="s">
-        <v>110</v>
+        <v>104007.0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="70">
-        <v>104008.0</v>
-      </c>
-      <c r="B80" s="71" t="s">
-        <v>197</v>
+      <c r="A80" s="73">
+        <v>104007.0</v>
+      </c>
+      <c r="B80" s="74" t="s">
+        <v>202</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="D80" s="6">
         <v>0.0</v>
       </c>
       <c r="E80" s="6">
-        <v>104009.0</v>
+        <v>104008.0</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P80" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="69">
-        <v>104009.0</v>
-      </c>
-      <c r="B81" s="71" t="s">
-        <v>198</v>
+      <c r="A81" s="73">
+        <v>104008.0</v>
+      </c>
+      <c r="B81" s="74" t="s">
+        <v>203</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D81" s="6">
         <v>0.0</v>
       </c>
       <c r="E81" s="6">
-        <v>104010.0</v>
+        <v>104009.0</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="P81" s="37" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="70">
-        <v>104010.0</v>
-      </c>
-      <c r="B82" s="71" t="s">
-        <v>199</v>
+      <c r="A82" s="72">
+        <v>104009.0</v>
+      </c>
+      <c r="B82" s="74" t="s">
+        <v>204</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D82" s="6">
         <v>0.0</v>
       </c>
       <c r="E82" s="6">
-        <v>104011.0</v>
-      </c>
-      <c r="O82" s="4" t="s">
-        <v>189</v>
+        <v>104010.0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="70">
-        <v>104011.0</v>
-      </c>
-      <c r="B83" s="71" t="s">
-        <v>200</v>
+      <c r="A83" s="73">
+        <v>104010.0</v>
+      </c>
+      <c r="B83" s="74" t="s">
+        <v>205</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D83" s="6">
         <v>0.0</v>
       </c>
       <c r="E83" s="6">
-        <v>104012.0</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>116</v>
+        <v>104011.0</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="70">
-        <v>104012.0</v>
-      </c>
-      <c r="B84" s="71" t="s">
-        <v>201</v>
+      <c r="A84" s="73">
+        <v>104011.0</v>
+      </c>
+      <c r="B84" s="74" t="s">
+        <v>206</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D84" s="6">
         <v>0.0</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>154</v>
+      <c r="E84" s="6">
+        <v>104012.0</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6">
-        <v>201001.0</v>
+      <c r="A85" s="73">
+        <v>104012.0</v>
       </c>
       <c r="B85" s="74" t="s">
-        <v>202</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>52</v>
+        <v>207</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D85" s="6">
         <v>0.0</v>
       </c>
-      <c r="E85" s="6">
-        <v>201002.0</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="32"/>
+      <c r="E85" s="6" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6">
-        <v>201002.0</v>
-      </c>
-      <c r="B86" s="74" t="s">
-        <v>205</v>
+        <v>201001.0</v>
+      </c>
+      <c r="B86" s="78" t="s">
+        <v>208</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>52</v>
@@ -14378,13 +14540,13 @@
         <v>0.0</v>
       </c>
       <c r="E86" s="6">
-        <v>201003.0</v>
+        <v>201002.0</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H86" s="32"/>
       <c r="I86" s="32"/>
@@ -14392,69 +14554,69 @@
     </row>
     <row r="87">
       <c r="A87" s="6">
-        <v>201003.0</v>
-      </c>
-      <c r="B87" s="74" t="s">
-        <v>206</v>
+        <v>201002.0</v>
+      </c>
+      <c r="B87" s="78" t="s">
+        <v>211</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>207</v>
+        <v>52</v>
       </c>
       <c r="D87" s="6">
         <v>0.0</v>
       </c>
       <c r="E87" s="6">
-        <v>201004.0</v>
+        <v>201003.0</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="H87" s="32"/>
-      <c r="I87" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="J87" s="60">
-        <v>0.05</v>
-      </c>
-      <c r="K87" s="60">
-        <v>-1.0</v>
-      </c>
+      <c r="I87" s="32"/>
+      <c r="J87" s="32"/>
     </row>
     <row r="88">
       <c r="A88" s="6">
-        <v>201004.0</v>
-      </c>
-      <c r="B88" s="74" t="s">
-        <v>208</v>
+        <v>201003.0</v>
+      </c>
+      <c r="B88" s="78" t="s">
+        <v>212</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>52</v>
+        <v>213</v>
       </c>
       <c r="D88" s="6">
         <v>0.0</v>
       </c>
       <c r="E88" s="6">
-        <v>201005.0</v>
+        <v>201004.0</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
-      <c r="J88" s="32"/>
+      <c r="I88" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="J88" s="60">
+        <v>0.05</v>
+      </c>
+      <c r="K88" s="60">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6">
-        <v>201005.0</v>
-      </c>
-      <c r="B89" s="74" t="s">
-        <v>210</v>
+        <v>201004.0</v>
+      </c>
+      <c r="B89" s="78" t="s">
+        <v>214</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>52</v>
@@ -14463,13 +14625,13 @@
         <v>0.0</v>
       </c>
       <c r="E89" s="6">
-        <v>201006.0</v>
+        <v>201005.0</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H89" s="32"/>
       <c r="I89" s="32"/>
@@ -14477,10 +14639,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6">
-        <v>201006.0</v>
-      </c>
-      <c r="B90" s="74" t="s">
-        <v>211</v>
+        <v>201005.0</v>
+      </c>
+      <c r="B90" s="78" t="s">
+        <v>216</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>52</v>
@@ -14489,67 +14651,64 @@
         <v>0.0</v>
       </c>
       <c r="E90" s="6">
-        <v>201007.0</v>
-      </c>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
+        <v>201006.0</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="H90" s="32"/>
       <c r="I90" s="32"/>
       <c r="J90" s="32"/>
     </row>
     <row r="91">
       <c r="A91" s="6">
-        <v>201007.0</v>
-      </c>
-      <c r="B91" s="74" t="s">
-        <v>212</v>
+        <v>201006.0</v>
+      </c>
+      <c r="B91" s="78" t="s">
+        <v>217</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>207</v>
+        <v>52</v>
       </c>
       <c r="D91" s="6">
         <v>0.0</v>
       </c>
       <c r="E91" s="6">
-        <v>201008.0</v>
+        <v>201007.0</v>
       </c>
       <c r="F91" s="32"/>
       <c r="G91" s="32"/>
       <c r="H91" s="32"/>
-      <c r="I91" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="J91" s="60">
-        <v>6.5</v>
-      </c>
-      <c r="K91" s="60">
-        <v>0.8</v>
-      </c>
+      <c r="I91" s="32"/>
+      <c r="J91" s="32"/>
     </row>
     <row r="92">
       <c r="A92" s="6">
-        <v>201008.0</v>
-      </c>
-      <c r="B92" s="74" t="s">
+        <v>201007.0</v>
+      </c>
+      <c r="B92" s="78" t="s">
+        <v>218</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="D92" s="6">
         <v>0.0</v>
       </c>
       <c r="E92" s="6">
-        <v>201009.0</v>
+        <v>201008.0</v>
       </c>
       <c r="F92" s="32"/>
       <c r="G92" s="32"/>
       <c r="H92" s="32"/>
       <c r="I92" s="60" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J92" s="60">
-        <v>6.0</v>
+        <v>6.5</v>
       </c>
       <c r="K92" s="60">
         <v>0.8</v>
@@ -14557,19 +14716,19 @@
     </row>
     <row r="93">
       <c r="A93" s="6">
-        <v>201009.0</v>
-      </c>
-      <c r="B93" s="74" t="s">
-        <v>214</v>
+        <v>201008.0</v>
+      </c>
+      <c r="B93" s="78" t="s">
+        <v>219</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="D93" s="6">
         <v>0.0</v>
       </c>
       <c r="E93" s="6">
-        <v>201010.0</v>
+        <v>201009.0</v>
       </c>
       <c r="F93" s="32"/>
       <c r="G93" s="32"/>
@@ -14578,83 +14737,86 @@
         <v>112</v>
       </c>
       <c r="J93" s="60">
-        <v>0.05</v>
-      </c>
-      <c r="K93" s="6">
-        <v>-1.0</v>
-      </c>
-      <c r="O93" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="P93" s="37" t="s">
-        <v>113</v>
+        <v>6.0</v>
+      </c>
+      <c r="K93" s="60">
+        <v>0.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6">
-        <v>201010.0</v>
-      </c>
-      <c r="B94" s="74" t="s">
-        <v>215</v>
+        <v>201009.0</v>
+      </c>
+      <c r="B94" s="78" t="s">
+        <v>220</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>207</v>
+        <v>111</v>
       </c>
       <c r="D94" s="6">
         <v>0.0</v>
       </c>
       <c r="E94" s="6">
-        <v>201011.0</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>204</v>
-      </c>
+        <v>201010.0</v>
+      </c>
+      <c r="F94" s="32"/>
+      <c r="G94" s="32"/>
       <c r="H94" s="32"/>
-      <c r="I94" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J94" s="6">
-        <v>7.0</v>
+      <c r="I94" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="J94" s="60">
+        <v>0.05</v>
       </c>
       <c r="K94" s="6">
-        <v>0.8</v>
+        <v>-1.0</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P94" s="37" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6">
-        <v>201011.0</v>
-      </c>
-      <c r="B95" s="75" t="s">
-        <v>216</v>
+        <v>201010.0</v>
+      </c>
+      <c r="B95" s="78" t="s">
+        <v>221</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>52</v>
+        <v>213</v>
       </c>
       <c r="D95" s="6">
         <v>0.0</v>
       </c>
       <c r="E95" s="6">
-        <v>201012.0</v>
+        <v>201011.0</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G95" s="76" t="s">
-        <v>102</v>
+        <v>215</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="H95" s="32"/>
-      <c r="I95" s="32"/>
-      <c r="J95" s="32"/>
+      <c r="I95" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J95" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="K95" s="6">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6">
-        <v>201012.0</v>
-      </c>
-      <c r="B96" s="74" t="s">
-        <v>217</v>
+        <v>201011.0</v>
+      </c>
+      <c r="B96" s="79" t="s">
+        <v>222</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>52</v>
@@ -14663,13 +14825,13 @@
         <v>0.0</v>
       </c>
       <c r="E96" s="6">
-        <v>201013.0</v>
+        <v>201012.0</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>204</v>
+        <v>104</v>
+      </c>
+      <c r="G96" s="80" t="s">
+        <v>105</v>
       </c>
       <c r="H96" s="32"/>
       <c r="I96" s="32"/>
@@ -14677,10 +14839,10 @@
     </row>
     <row r="97">
       <c r="A97" s="6">
-        <v>201013.0</v>
-      </c>
-      <c r="B97" s="74" t="s">
-        <v>218</v>
+        <v>201012.0</v>
+      </c>
+      <c r="B97" s="78" t="s">
+        <v>223</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>52</v>
@@ -14689,13 +14851,13 @@
         <v>0.0</v>
       </c>
       <c r="E97" s="6">
-        <v>201014.0</v>
+        <v>201013.0</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="32"/>
@@ -14703,10 +14865,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6">
-        <v>201014.0</v>
-      </c>
-      <c r="B98" s="74" t="s">
-        <v>220</v>
+        <v>201013.0</v>
+      </c>
+      <c r="B98" s="78" t="s">
+        <v>224</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>52</v>
@@ -14715,13 +14877,13 @@
         <v>0.0</v>
       </c>
       <c r="E98" s="6">
-        <v>201015.0</v>
+        <v>201014.0</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="H98" s="32"/>
       <c r="I98" s="32"/>
@@ -14729,10 +14891,10 @@
     </row>
     <row r="99">
       <c r="A99" s="6">
-        <v>201015.0</v>
-      </c>
-      <c r="B99" s="74" t="s">
-        <v>221</v>
+        <v>201014.0</v>
+      </c>
+      <c r="B99" s="78" t="s">
+        <v>226</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>52</v>
@@ -14741,55 +14903,59 @@
         <v>0.0</v>
       </c>
       <c r="E99" s="6">
-        <v>201016.0</v>
+        <v>201015.0</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="32"/>
       <c r="J99" s="32"/>
     </row>
     <row r="100">
-      <c r="A100" s="69">
-        <v>201016.0</v>
-      </c>
-      <c r="B100" s="74" t="s">
-        <v>222</v>
+      <c r="A100" s="6">
+        <v>201015.0</v>
+      </c>
+      <c r="B100" s="78" t="s">
+        <v>227</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="D100" s="6">
         <v>0.0</v>
       </c>
       <c r="E100" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
+        <v>201016.0</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="H100" s="32"/>
       <c r="I100" s="32"/>
       <c r="J100" s="32"/>
     </row>
     <row r="101">
-      <c r="A101" s="69">
-        <v>2010161.0</v>
-      </c>
-      <c r="B101" s="74" t="s">
-        <v>223</v>
+      <c r="A101" s="72">
+        <v>201016.0</v>
+      </c>
+      <c r="B101" s="78" t="s">
+        <v>228</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
       <c r="D101" s="6">
         <v>0.0</v>
       </c>
       <c r="E101" s="6">
-        <v>201017.0</v>
+        <v>0.0</v>
       </c>
       <c r="F101" s="32"/>
       <c r="G101" s="32"/>
@@ -14798,11 +14964,11 @@
       <c r="J101" s="32"/>
     </row>
     <row r="102">
-      <c r="A102" s="69">
-        <v>2010162.0</v>
-      </c>
-      <c r="B102" s="74" t="s">
-        <v>224</v>
+      <c r="A102" s="72">
+        <v>2010161.0</v>
+      </c>
+      <c r="B102" s="78" t="s">
+        <v>229</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>52</v>
@@ -14811,7 +14977,7 @@
         <v>0.0</v>
       </c>
       <c r="E102" s="6">
-        <v>201019.0</v>
+        <v>201017.0</v>
       </c>
       <c r="F102" s="32"/>
       <c r="G102" s="32"/>
@@ -14820,11 +14986,11 @@
       <c r="J102" s="32"/>
     </row>
     <row r="103">
-      <c r="A103" s="69">
-        <v>201017.0</v>
-      </c>
-      <c r="B103" s="74" t="s">
-        <v>225</v>
+      <c r="A103" s="72">
+        <v>2010162.0</v>
+      </c>
+      <c r="B103" s="78" t="s">
+        <v>230</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>52</v>
@@ -14833,24 +14999,20 @@
         <v>0.0</v>
       </c>
       <c r="E103" s="6">
-        <v>201018.0</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>204</v>
-      </c>
+        <v>201019.0</v>
+      </c>
+      <c r="F103" s="32"/>
+      <c r="G103" s="32"/>
       <c r="H103" s="32"/>
       <c r="I103" s="32"/>
       <c r="J103" s="32"/>
     </row>
     <row r="104">
-      <c r="A104" s="69">
-        <v>201018.0</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>226</v>
+      <c r="A104" s="72">
+        <v>201017.0</v>
+      </c>
+      <c r="B104" s="78" t="s">
+        <v>231</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>52</v>
@@ -14859,24 +15021,24 @@
         <v>0.0</v>
       </c>
       <c r="E104" s="6">
-        <v>201016.0</v>
+        <v>201018.0</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H104" s="32"/>
       <c r="I104" s="32"/>
       <c r="J104" s="32"/>
     </row>
     <row r="105">
-      <c r="A105" s="69">
-        <v>201019.0</v>
+      <c r="A105" s="72">
+        <v>201018.0</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>52</v>
@@ -14885,24 +15047,24 @@
         <v>0.0</v>
       </c>
       <c r="E105" s="6">
-        <v>201020.0</v>
+        <v>201016.0</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="32"/>
       <c r="J105" s="32"/>
     </row>
     <row r="106">
-      <c r="A106" s="69">
-        <v>201020.0</v>
+      <c r="A106" s="72">
+        <v>201019.0</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>52</v>
@@ -14911,24 +15073,24 @@
         <v>0.0</v>
       </c>
       <c r="E106" s="6">
-        <v>201016.0</v>
+        <v>201020.0</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H106" s="32"/>
       <c r="I106" s="32"/>
       <c r="J106" s="32"/>
     </row>
     <row r="107">
-      <c r="A107" s="6">
-        <v>201021.0</v>
-      </c>
-      <c r="B107" s="74" t="s">
-        <v>229</v>
+      <c r="A107" s="72">
+        <v>201020.0</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>52</v>
@@ -14937,13 +15099,13 @@
         <v>0.0</v>
       </c>
       <c r="E107" s="6">
-        <v>201022.0</v>
+        <v>201016.0</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G107" s="76" t="s">
-        <v>107</v>
+        <v>215</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="H107" s="32"/>
       <c r="I107" s="32"/>
@@ -14951,10 +15113,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6">
-        <v>201022.0</v>
-      </c>
-      <c r="B108" s="74" t="s">
-        <v>230</v>
+        <v>201021.0</v>
+      </c>
+      <c r="B108" s="78" t="s">
+        <v>235</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>52</v>
@@ -14963,13 +15125,13 @@
         <v>0.0</v>
       </c>
       <c r="E108" s="6">
-        <v>201023.0</v>
+        <v>201022.0</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>204</v>
+        <v>104</v>
+      </c>
+      <c r="G108" s="80" t="s">
+        <v>110</v>
       </c>
       <c r="H108" s="32"/>
       <c r="I108" s="32"/>
@@ -14977,10 +15139,10 @@
     </row>
     <row r="109">
       <c r="A109" s="6">
-        <v>201023.0</v>
-      </c>
-      <c r="B109" s="74" t="s">
-        <v>231</v>
+        <v>201022.0</v>
+      </c>
+      <c r="B109" s="78" t="s">
+        <v>236</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>52</v>
@@ -14989,13 +15151,13 @@
         <v>0.0</v>
       </c>
       <c r="E109" s="6">
-        <v>201024.0</v>
+        <v>201023.0</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H109" s="32"/>
       <c r="I109" s="32"/>
@@ -15003,10 +15165,10 @@
     </row>
     <row r="110">
       <c r="A110" s="6">
-        <v>201024.0</v>
-      </c>
-      <c r="B110" s="74" t="s">
-        <v>232</v>
+        <v>201023.0</v>
+      </c>
+      <c r="B110" s="78" t="s">
+        <v>237</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>52</v>
@@ -15015,13 +15177,13 @@
         <v>0.0</v>
       </c>
       <c r="E110" s="6">
-        <v>201025.0</v>
+        <v>201024.0</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="H110" s="32"/>
       <c r="I110" s="32"/>
@@ -15029,10 +15191,10 @@
     </row>
     <row r="111">
       <c r="A111" s="6">
-        <v>201025.0</v>
-      </c>
-      <c r="B111" s="74" t="s">
-        <v>233</v>
+        <v>201024.0</v>
+      </c>
+      <c r="B111" s="78" t="s">
+        <v>238</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>52</v>
@@ -15041,13 +15203,13 @@
         <v>0.0</v>
       </c>
       <c r="E111" s="6">
-        <v>201026.0</v>
+        <v>201025.0</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="H111" s="32"/>
       <c r="I111" s="32"/>
@@ -15055,10 +15217,10 @@
     </row>
     <row r="112">
       <c r="A112" s="6">
-        <v>201026.0</v>
-      </c>
-      <c r="B112" s="74" t="s">
-        <v>234</v>
+        <v>201025.0</v>
+      </c>
+      <c r="B112" s="78" t="s">
+        <v>239</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>52</v>
@@ -15067,13 +15229,13 @@
         <v>0.0</v>
       </c>
       <c r="E112" s="6">
-        <v>201027.0</v>
+        <v>201026.0</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H112" s="32"/>
       <c r="I112" s="32"/>
@@ -15081,10 +15243,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6">
-        <v>201027.0</v>
-      </c>
-      <c r="B113" s="74" t="s">
-        <v>235</v>
+        <v>201026.0</v>
+      </c>
+      <c r="B113" s="78" t="s">
+        <v>240</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>52</v>
@@ -15093,13 +15255,13 @@
         <v>0.0</v>
       </c>
       <c r="E113" s="6">
-        <v>201028.0</v>
+        <v>201027.0</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="H113" s="32"/>
       <c r="I113" s="32"/>
@@ -15107,10 +15269,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6">
-        <v>201028.0</v>
-      </c>
-      <c r="B114" s="74" t="s">
-        <v>236</v>
+        <v>201027.0</v>
+      </c>
+      <c r="B114" s="78" t="s">
+        <v>241</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>52</v>
@@ -15119,13 +15281,13 @@
         <v>0.0</v>
       </c>
       <c r="E114" s="6">
-        <v>201029.0</v>
+        <v>201028.0</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="32"/>
@@ -15133,10 +15295,10 @@
     </row>
     <row r="115">
       <c r="A115" s="6">
-        <v>201029.0</v>
-      </c>
-      <c r="B115" s="74" t="s">
-        <v>237</v>
+        <v>201028.0</v>
+      </c>
+      <c r="B115" s="78" t="s">
+        <v>242</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>52</v>
@@ -15145,13 +15307,13 @@
         <v>0.0</v>
       </c>
       <c r="E115" s="6">
-        <v>201030.0</v>
+        <v>201029.0</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H115" s="32"/>
       <c r="I115" s="32"/>
@@ -15159,10 +15321,10 @@
     </row>
     <row r="116">
       <c r="A116" s="6">
-        <v>201030.0</v>
-      </c>
-      <c r="B116" s="74" t="s">
-        <v>238</v>
+        <v>201029.0</v>
+      </c>
+      <c r="B116" s="78" t="s">
+        <v>243</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>52</v>
@@ -15171,13 +15333,13 @@
         <v>0.0</v>
       </c>
       <c r="E116" s="6">
-        <v>201031.0</v>
+        <v>201030.0</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="H116" s="32"/>
       <c r="I116" s="32"/>
@@ -15185,10 +15347,10 @@
     </row>
     <row r="117">
       <c r="A117" s="6">
-        <v>201031.0</v>
-      </c>
-      <c r="B117" s="74" t="s">
-        <v>239</v>
+        <v>201030.0</v>
+      </c>
+      <c r="B117" s="78" t="s">
+        <v>244</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>52</v>
@@ -15197,13 +15359,13 @@
         <v>0.0</v>
       </c>
       <c r="E117" s="6">
-        <v>201032.0</v>
+        <v>201031.0</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="H117" s="32"/>
       <c r="I117" s="32"/>
@@ -15211,10 +15373,10 @@
     </row>
     <row r="118">
       <c r="A118" s="6">
-        <v>201032.0</v>
-      </c>
-      <c r="B118" s="74" t="s">
-        <v>240</v>
+        <v>201031.0</v>
+      </c>
+      <c r="B118" s="78" t="s">
+        <v>245</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>52</v>
@@ -15223,13 +15385,13 @@
         <v>0.0</v>
       </c>
       <c r="E118" s="6">
-        <v>201033.0</v>
+        <v>201032.0</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="32"/>
@@ -15237,10 +15399,10 @@
     </row>
     <row r="119">
       <c r="A119" s="6">
-        <v>201033.0</v>
-      </c>
-      <c r="B119" s="74" t="s">
-        <v>241</v>
+        <v>201032.0</v>
+      </c>
+      <c r="B119" s="78" t="s">
+        <v>246</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>52</v>
@@ -15249,13 +15411,13 @@
         <v>0.0</v>
       </c>
       <c r="E119" s="6">
-        <v>201034.0</v>
+        <v>201033.0</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H119" s="32"/>
       <c r="I119" s="32"/>
@@ -15263,10 +15425,10 @@
     </row>
     <row r="120">
       <c r="A120" s="6">
-        <v>201034.0</v>
-      </c>
-      <c r="B120" s="74" t="s">
-        <v>242</v>
+        <v>201033.0</v>
+      </c>
+      <c r="B120" s="78" t="s">
+        <v>247</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>52</v>
@@ -15275,229 +15437,243 @@
         <v>0.0</v>
       </c>
       <c r="E120" s="6">
-        <v>201035.0</v>
+        <v>201034.0</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="32"/>
       <c r="J120" s="32"/>
     </row>
     <row r="121">
-      <c r="A121" s="69">
-        <v>201035.0</v>
-      </c>
-      <c r="B121" s="74" t="s">
-        <v>243</v>
+      <c r="A121" s="6">
+        <v>201034.0</v>
+      </c>
+      <c r="B121" s="78" t="s">
+        <v>248</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D121" s="6">
         <v>0.0</v>
       </c>
       <c r="E121" s="6">
-        <v>201036.0</v>
-      </c>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
+        <v>201035.0</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G121" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="H121" s="32"/>
       <c r="I121" s="32"/>
       <c r="J121" s="32"/>
     </row>
     <row r="122">
-      <c r="A122" s="6">
-        <v>201036.0</v>
-      </c>
-      <c r="B122" s="74" t="s">
-        <v>244</v>
+      <c r="A122" s="72">
+        <v>201035.0</v>
+      </c>
+      <c r="B122" s="78" t="s">
+        <v>249</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D122" s="6">
         <v>0.0</v>
       </c>
       <c r="E122" s="6">
-        <v>201037.0</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>204</v>
-      </c>
+        <v>201036.0</v>
+      </c>
+      <c r="F122" s="6"/>
+      <c r="G122" s="6"/>
       <c r="H122" s="32"/>
       <c r="I122" s="32"/>
       <c r="J122" s="32"/>
     </row>
     <row r="123">
       <c r="A123" s="6">
-        <v>201037.0</v>
-      </c>
-      <c r="B123" s="74" t="s">
-        <v>245</v>
+        <v>201036.0</v>
+      </c>
+      <c r="B123" s="78" t="s">
+        <v>250</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D123" s="6">
         <v>0.0</v>
       </c>
       <c r="E123" s="6">
-        <v>201038.0</v>
-      </c>
-      <c r="F123" s="32"/>
-      <c r="G123" s="32"/>
+        <v>201037.0</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G123" s="6" t="s">
+        <v>210</v>
+      </c>
       <c r="H123" s="32"/>
       <c r="I123" s="32"/>
       <c r="J123" s="32"/>
     </row>
     <row r="124">
       <c r="A124" s="6">
-        <v>201038.0</v>
-      </c>
-      <c r="B124" s="74" t="s">
-        <v>246</v>
+        <v>201037.0</v>
+      </c>
+      <c r="B124" s="78" t="s">
+        <v>251</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D124" s="6">
         <v>0.0</v>
       </c>
       <c r="E124" s="6">
-        <v>201039.0</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>107</v>
-      </c>
+        <v>201038.0</v>
+      </c>
+      <c r="F124" s="32"/>
+      <c r="G124" s="32"/>
       <c r="H124" s="32"/>
       <c r="I124" s="32"/>
       <c r="J124" s="32"/>
     </row>
     <row r="125">
       <c r="A125" s="6">
-        <v>201039.0</v>
-      </c>
-      <c r="B125" s="74" t="s">
-        <v>247</v>
+        <v>201038.0</v>
+      </c>
+      <c r="B125" s="78" t="s">
+        <v>252</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D125" s="6">
         <v>0.0</v>
       </c>
       <c r="E125" s="6">
-        <v>201040.0</v>
-      </c>
-      <c r="F125" s="32"/>
-      <c r="G125" s="32"/>
+        <v>201039.0</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="H125" s="32"/>
       <c r="I125" s="32"/>
       <c r="J125" s="32"/>
     </row>
     <row r="126">
       <c r="A126" s="6">
-        <v>201040.0</v>
-      </c>
-      <c r="B126" s="74" t="s">
-        <v>248</v>
+        <v>201039.0</v>
+      </c>
+      <c r="B126" s="78" t="s">
+        <v>253</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="D126" s="6">
         <v>0.0</v>
       </c>
       <c r="E126" s="6">
-        <v>201041.0</v>
+        <v>201040.0</v>
       </c>
       <c r="F126" s="32"/>
       <c r="G126" s="32"/>
-      <c r="H126" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="I126" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="J126" s="60">
-        <v>6.0</v>
-      </c>
-      <c r="K126" s="60">
-        <v>2.0</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="P126" s="37" t="s">
-        <v>110</v>
-      </c>
+      <c r="H126" s="32"/>
+      <c r="I126" s="32"/>
+      <c r="J126" s="32"/>
     </row>
     <row r="127">
       <c r="A127" s="6">
-        <v>201041.0</v>
-      </c>
-      <c r="B127" s="74" t="s">
-        <v>250</v>
+        <v>201040.0</v>
+      </c>
+      <c r="B127" s="78" t="s">
+        <v>254</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="D127" s="6">
         <v>0.0</v>
       </c>
       <c r="E127" s="6">
-        <v>201042.0</v>
+        <v>201041.0</v>
       </c>
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
-      <c r="H127" s="32"/>
-      <c r="I127" s="32"/>
-      <c r="J127" s="32"/>
+      <c r="H127" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I127" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="J127" s="60">
+        <v>6.0</v>
+      </c>
+      <c r="K127" s="60">
+        <v>2.0</v>
+      </c>
       <c r="O127" s="6" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="P127" s="37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6">
-        <v>201042.0</v>
-      </c>
-      <c r="B128" s="77" t="s">
-        <v>201</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>18</v>
+        <v>201041.0</v>
+      </c>
+      <c r="B128" s="78" t="s">
+        <v>256</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="D128" s="6">
         <v>0.0</v>
       </c>
-      <c r="E128" s="6" t="s">
-        <v>154</v>
+      <c r="E128" s="6">
+        <v>201042.0</v>
       </c>
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>
       <c r="H128" s="32"/>
       <c r="I128" s="32"/>
       <c r="J128" s="32"/>
+      <c r="O128" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P128" s="37" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="32"/>
-      <c r="B129" s="77"/>
-      <c r="C129" s="32"/>
-      <c r="D129" s="32"/>
-      <c r="E129" s="32"/>
+      <c r="A129" s="6">
+        <v>201042.0</v>
+      </c>
+      <c r="B129" s="81" t="s">
+        <v>207</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D129" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>161</v>
+      </c>
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
       <c r="H129" s="32"/>
@@ -15506,7 +15682,7 @@
     </row>
     <row r="130">
       <c r="A130" s="32"/>
-      <c r="B130" s="32"/>
+      <c r="B130" s="81"/>
       <c r="C130" s="32"/>
       <c r="D130" s="32"/>
       <c r="E130" s="32"/>
@@ -15612,6 +15788,18 @@
       <c r="I138" s="32"/>
       <c r="J138" s="32"/>
     </row>
+    <row r="139">
+      <c r="A139" s="32"/>
+      <c r="B139" s="32"/>
+      <c r="C139" s="32"/>
+      <c r="D139" s="32"/>
+      <c r="E139" s="32"/>
+      <c r="F139" s="32"/>
+      <c r="G139" s="32"/>
+      <c r="H139" s="32"/>
+      <c r="I139" s="32"/>
+      <c r="J139" s="32"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="261">
   <si>
     <t>To. 개발 : 스크립트 수정 시, 파란색으로 칠해둘 것!!</t>
   </si>
@@ -810,6 +810,15 @@
     <t>{fade a=3.5}아쉽지만, 나는 죄를 지어 이 구천에 갇혀 &lt;b&gt;영원히 인연의 실들을 엮는 물레&lt;/b&gt;를 돌리고 있단다.</t>
   </si>
   <si>
+    <t>Script, Animation</t>
+  </si>
+  <si>
+    <t>Yeonong</t>
+  </si>
+  <si>
+    <t>Yeon_wheel</t>
+  </si>
+  <si>
     <t>{fade a=3.5}즉, 지금의 나에게는 너를 도울만한 힘이 없다는 것이지.</t>
   </si>
   <si>
@@ -846,25 +855,28 @@
     <t xml:space="preserve">{fade a=3.5}자 이 아이를 따라가거라. </t>
   </si>
   <si>
-    <t>고양이 뛰어나감</t>
-  </si>
-  <si>
-    <t>{fade a=3.5}이 곳을 빠져나가는데 도움을 줄 수 있을 것이야.</t>
-  </si>
-  <si>
-    <t>(안나에게 다가온 고양이가 안나의 다리에 머리를 비비며 친근감을 나타낸다)고양이에게 쉬프트</t>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>고양이 걸어나가서 &amp; 안나 앞에 앉음</t>
+  </si>
+  <si>
+    <t>{fade a=3.5}이 아이가 도움을 줄 수 있을 것이야.</t>
+  </si>
+  <si>
+    <t>C5_hand</t>
   </si>
   <si>
     <t>{fade a=3.5}!! 감사합니다…!! 이 은혜를 잊지 않을게요…!!!</t>
   </si>
   <si>
-    <t>안나가 오른쪽으로 걸어나간다. (카메라 아웃)</t>
+    <t>연옹 카메라 쉬프트</t>
+  </si>
+  <si>
+    <t>안나와 고양이가 함께 오른쪽으로 걸어나간다. (카메라 아웃)</t>
   </si>
   <si>
     <t xml:space="preserve">{fade a=3.5}그래 이 정도면 충분하지 않느냐? </t>
-  </si>
-  <si>
-    <t>Yeonong</t>
   </si>
   <si>
     <t>{fade a=3.5}그렇지 웅단아?</t>
@@ -1422,7 +1434,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1450,7 +1462,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2881,7 +2893,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="34"/>
+      <c r="D40" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102002.0)</f>
+        <v>102002</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="34">
@@ -2896,7 +2911,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="34"/>
+      <c r="D41" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102003.0)</f>
+        <v>102003</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="34">
@@ -2911,7 +2929,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="34"/>
+      <c r="D42" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102004.0)</f>
+        <v>102004</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="34">
@@ -2926,7 +2947,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="34"/>
+      <c r="D43" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102005.0)</f>
+        <v>102005</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="34">
@@ -2941,7 +2965,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="34"/>
+      <c r="D44" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),102006.0)</f>
+        <v>102006</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="34">
@@ -4092,8 +4119,8 @@
         <v>201022</v>
       </c>
       <c r="B109" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Animation")</f>
+        <v>Script, Animation</v>
       </c>
       <c r="C109" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4110,8 +4137,8 @@
         <v>201023</v>
       </c>
       <c r="B110" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Animation")</f>
+        <v>Script, Animation</v>
       </c>
       <c r="C110" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4308,8 +4335,8 @@
         <v>201034</v>
       </c>
       <c r="B121" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Camera")</f>
+        <v>Script, Camera</v>
       </c>
       <c r="C121" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4344,8 +4371,8 @@
         <v>201036</v>
       </c>
       <c r="B123" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script, Animation")</f>
+        <v>Script, Animation</v>
       </c>
       <c r="C123" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4362,8 +4389,8 @@
         <v>201037</v>
       </c>
       <c r="B124" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
-        <v>Camera</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
+        <v>Script</v>
       </c>
       <c r="C124" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4380,8 +4407,8 @@
         <v>201038</v>
       </c>
       <c r="B125" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Script")</f>
-        <v>Script</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C125" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -10615,14 +10642,14 @@
         <v>Yeonong_Idle</v>
       </c>
       <c r="D48" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}이 곳을 빠져나가는데 도움을 줄 수 있을 것이야.")</f>
-        <v>{fade a=3.5}이 곳을 빠져나가는데 도움을 줄 수 있을 것이야.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}이 아이가 도움을 줄 수 있을 것이야.")</f>
+        <v>{fade a=3.5}이 아이가 도움을 줄 수 있을 것이야.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201038.0)</f>
-        <v>201038</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
+        <v>201037</v>
       </c>
       <c r="B49" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"안나")</f>
@@ -11062,8 +11089,8 @@
         <v>0.1</v>
       </c>
       <c r="E22" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -11202,8 +11229,8 @@
         <v>0.05</v>
       </c>
       <c r="E30" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="31">
@@ -11259,8 +11286,8 @@
         <v>0.05</v>
       </c>
       <c r="E33" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),-1.0)</f>
-        <v>-1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
@@ -11288,38 +11315,69 @@
         <v>201016</v>
       </c>
       <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
+      <c r="C35" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
+        <v>ZoomIn</v>
+      </c>
+      <c r="D35" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="E35" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201037.0)</f>
-        <v>201037</v>
-      </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201034.0)</f>
+        <v>201034</v>
+      </c>
+      <c r="B36" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"C5")</f>
+        <v>C5</v>
+      </c>
+      <c r="C36" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
+        <v>CameraShift</v>
+      </c>
       <c r="D36" s="34"/>
       <c r="E36" s="34"/>
     </row>
     <row r="37">
       <c r="A37" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
-        <v>201040</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201038.0)</f>
+        <v>201038</v>
       </c>
       <c r="B37" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeonong")</f>
         <v>Yeonong</v>
       </c>
       <c r="C37" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CameraShift")</f>
+        <v>CameraShift</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
+        <v>201040</v>
+      </c>
+      <c r="B38" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeonong")</f>
+        <v>Yeonong</v>
+      </c>
+      <c r="C38" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
         <v>ZoomIn</v>
       </c>
-      <c r="D37" s="34">
+      <c r="D38" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0)</f>
         <v>6</v>
       </c>
-      <c r="E37" s="34">
+      <c r="E38" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
@@ -11680,6 +11738,60 @@
       <c r="D19" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Left")</f>
         <v>Left</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201022.0)</f>
+        <v>201022</v>
+      </c>
+      <c r="B20" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeonong")</f>
+        <v>Yeonong</v>
+      </c>
+      <c r="C20" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeon_wheel")</f>
+        <v>Yeon_wheel</v>
+      </c>
+      <c r="D20" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
+        <v>Right</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201023.0)</f>
+        <v>201023</v>
+      </c>
+      <c r="B21" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeonong")</f>
+        <v>Yeonong</v>
+      </c>
+      <c r="C21" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeon_wheel")</f>
+        <v>Yeon_wheel</v>
+      </c>
+      <c r="D21" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
+        <v>Right</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201036.0)</f>
+        <v>201036</v>
+      </c>
+      <c r="B22" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"C5")</f>
+        <v>C5</v>
+      </c>
+      <c r="C22" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"C5_hand")</f>
+        <v>C5_hand</v>
+      </c>
+      <c r="D22" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
+        <v>Right</v>
       </c>
     </row>
   </sheetData>
@@ -12133,8 +12245,8 @@
         <v>어떻게 할까?</v>
       </c>
       <c r="C3" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Obstacle_H")</f>
-        <v>Obstacle_H</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
+        <v>Anna</v>
       </c>
       <c r="D3" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
@@ -13514,6 +13626,9 @@
       <c r="D40" s="6">
         <v>0.0</v>
       </c>
+      <c r="E40" s="4">
+        <v>102002.0</v>
+      </c>
       <c r="I40" s="61" t="s">
         <v>112</v>
       </c>
@@ -13537,6 +13652,9 @@
       <c r="D41" s="6">
         <v>0.0</v>
       </c>
+      <c r="E41" s="4">
+        <v>102003.0</v>
+      </c>
       <c r="H41" s="4" t="s">
         <v>118</v>
       </c>
@@ -13560,6 +13678,9 @@
       <c r="D42" s="6">
         <v>0.0</v>
       </c>
+      <c r="E42" s="4">
+        <v>102004.0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="73">
@@ -13574,6 +13695,9 @@
       <c r="D43" s="6">
         <v>0.0</v>
       </c>
+      <c r="E43" s="4">
+        <v>102005.0</v>
+      </c>
       <c r="H43" s="4" t="s">
         <v>21</v>
       </c>
@@ -13593,6 +13717,9 @@
       </c>
       <c r="D44" s="6">
         <v>0.0</v>
+      </c>
+      <c r="E44" s="4">
+        <v>102006.0</v>
       </c>
       <c r="I44" s="61" t="s">
         <v>149</v>
@@ -14137,7 +14264,7 @@
         <v>0.1</v>
       </c>
       <c r="K68" s="60">
-        <v>-1.0</v>
+        <v>0.8</v>
       </c>
       <c r="N68" s="55"/>
       <c r="O68" s="4" t="s">
@@ -14357,7 +14484,7 @@
       <c r="J77" s="60"/>
       <c r="K77" s="60"/>
       <c r="Q77" s="4" t="s">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="R77" s="4">
         <v>2.0</v>
@@ -14608,7 +14735,7 @@
         <v>0.05</v>
       </c>
       <c r="K88" s="60">
-        <v>-1.0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="89">
@@ -14769,7 +14896,7 @@
         <v>0.05</v>
       </c>
       <c r="K94" s="6">
-        <v>-1.0</v>
+        <v>0.8</v>
       </c>
       <c r="O94" s="4" t="s">
         <v>21</v>
@@ -14960,8 +15087,15 @@
       <c r="F101" s="32"/>
       <c r="G101" s="32"/>
       <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
-      <c r="J101" s="32"/>
+      <c r="I101" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="J101" s="60">
+        <v>6.0</v>
+      </c>
+      <c r="K101" s="60">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="72">
@@ -15030,8 +15164,15 @@
         <v>210</v>
       </c>
       <c r="H104" s="32"/>
-      <c r="I104" s="32"/>
-      <c r="J104" s="32"/>
+      <c r="I104" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J104" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="K104" s="6">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="72">
@@ -15082,8 +15223,15 @@
         <v>210</v>
       </c>
       <c r="H106" s="32"/>
-      <c r="I106" s="32"/>
-      <c r="J106" s="32"/>
+      <c r="I106" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J106" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="K106" s="6">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="72">
@@ -15145,7 +15293,7 @@
         <v>236</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>52</v>
+        <v>237</v>
       </c>
       <c r="D109" s="6">
         <v>0.0</v>
@@ -15162,16 +15310,25 @@
       <c r="H109" s="32"/>
       <c r="I109" s="32"/>
       <c r="J109" s="32"/>
+      <c r="L109" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="M109" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N109" s="55" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6">
         <v>201023.0</v>
       </c>
       <c r="B110" s="78" t="s">
+        <v>240</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D110" s="6">
         <v>0.0</v>
@@ -15188,13 +15345,22 @@
       <c r="H110" s="32"/>
       <c r="I110" s="32"/>
       <c r="J110" s="32"/>
+      <c r="L110" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="M110" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="N110" s="55" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6">
         <v>201024.0</v>
       </c>
       <c r="B111" s="78" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>52</v>
@@ -15220,7 +15386,7 @@
         <v>201025.0</v>
       </c>
       <c r="B112" s="78" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>52</v>
@@ -15246,7 +15412,7 @@
         <v>201026.0</v>
       </c>
       <c r="B113" s="78" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>52</v>
@@ -15272,7 +15438,7 @@
         <v>201027.0</v>
       </c>
       <c r="B114" s="78" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>52</v>
@@ -15298,7 +15464,7 @@
         <v>201028.0</v>
       </c>
       <c r="B115" s="78" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>52</v>
@@ -15324,7 +15490,7 @@
         <v>201029.0</v>
       </c>
       <c r="B116" s="78" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>52</v>
@@ -15350,7 +15516,7 @@
         <v>201030.0</v>
       </c>
       <c r="B117" s="78" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>52</v>
@@ -15376,7 +15542,7 @@
         <v>201031.0</v>
       </c>
       <c r="B118" s="78" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>52</v>
@@ -15402,7 +15568,7 @@
         <v>201032.0</v>
       </c>
       <c r="B119" s="78" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>52</v>
@@ -15428,7 +15594,7 @@
         <v>201033.0</v>
       </c>
       <c r="B120" s="78" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>52</v>
@@ -15454,10 +15620,10 @@
         <v>201034.0</v>
       </c>
       <c r="B121" s="78" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>52</v>
+        <v>213</v>
       </c>
       <c r="D121" s="6">
         <v>0.0</v>
@@ -15471,8 +15637,12 @@
       <c r="G121" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="H121" s="32"/>
-      <c r="I121" s="32"/>
+      <c r="H121" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="J121" s="32"/>
     </row>
     <row r="122">
@@ -15480,7 +15650,7 @@
         <v>201035.0</v>
       </c>
       <c r="B122" s="78" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>40</v>
@@ -15502,10 +15672,10 @@
         <v>201036.0</v>
       </c>
       <c r="B123" s="78" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>52</v>
+        <v>237</v>
       </c>
       <c r="D123" s="6">
         <v>0.0</v>
@@ -15522,16 +15692,25 @@
       <c r="H123" s="32"/>
       <c r="I123" s="32"/>
       <c r="J123" s="32"/>
+      <c r="L123" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="M123" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="N123" s="55" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="6">
         <v>201037.0</v>
       </c>
       <c r="B124" s="78" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D124" s="6">
         <v>0.0</v>
@@ -15539,10 +15718,18 @@
       <c r="E124" s="6">
         <v>201038.0</v>
       </c>
-      <c r="F124" s="32"/>
-      <c r="G124" s="32"/>
-      <c r="H124" s="32"/>
-      <c r="I124" s="32"/>
+      <c r="F124" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="J124" s="32"/>
     </row>
     <row r="125">
@@ -15550,10 +15737,10 @@
         <v>201038.0</v>
       </c>
       <c r="B125" s="78" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D125" s="6">
         <v>0.0</v>
@@ -15561,22 +15748,22 @@
       <c r="E125" s="6">
         <v>201039.0</v>
       </c>
-      <c r="F125" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G125" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="H125" s="32"/>
-      <c r="I125" s="32"/>
+      <c r="F125" s="6"/>
+      <c r="G125" s="6"/>
+      <c r="H125" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="J125" s="32"/>
     </row>
     <row r="126">
-      <c r="A126" s="6">
+      <c r="A126" s="72">
         <v>201039.0</v>
       </c>
       <c r="B126" s="78" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>40</v>
@@ -15598,7 +15785,7 @@
         <v>201040.0</v>
       </c>
       <c r="B127" s="78" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>111</v>
@@ -15612,7 +15799,7 @@
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
       <c r="H127" s="6" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="I127" s="60" t="s">
         <v>112</v>
@@ -15624,7 +15811,7 @@
         <v>2.0</v>
       </c>
       <c r="O127" s="6" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="P127" s="37" t="s">
         <v>113</v>
@@ -15635,7 +15822,7 @@
         <v>201041.0</v>
       </c>
       <c r="B128" s="78" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>55</v>
@@ -15652,7 +15839,7 @@
       <c r="I128" s="32"/>
       <c r="J128" s="32"/>
       <c r="O128" s="6" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="P128" s="37" t="s">
         <v>113</v>

--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -1406,7 +1406,7 @@
     <xdr:ext cx="3524250" cy="695325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1434,7 +1434,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1462,7 +1462,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4465,8 +4465,8 @@
         <v>Bubble</v>
       </c>
       <c r="C128" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="D128" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
@@ -11365,10 +11365,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201040.0)</f>
         <v>201040</v>
       </c>
-      <c r="B38" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Yeonong")</f>
-        <v>Yeonong</v>
-      </c>
+      <c r="B38" s="34"/>
       <c r="C38" s="34" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ZoomIn")</f>
         <v>ZoomIn</v>
@@ -11754,8 +11751,8 @@
         <v>Yeon_wheel</v>
       </c>
       <c r="D20" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
-        <v>Right</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Left")</f>
+        <v>Left</v>
       </c>
     </row>
     <row r="21">
@@ -11772,8 +11769,8 @@
         <v>Yeon_wheel</v>
       </c>
       <c r="D21" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Right")</f>
-        <v>Right</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Left")</f>
+        <v>Left</v>
       </c>
     </row>
     <row r="22">
@@ -12262,8 +12259,14 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"무엇을 물을까?")</f>
         <v>무엇을 물을까?</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
+      <c r="C4" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Anna")</f>
+        <v>Anna</v>
+      </c>
+      <c r="D4" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -15055,7 +15058,7 @@
       <c r="D100" s="6">
         <v>0.0</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="72">
         <v>201016.0</v>
       </c>
       <c r="F100" s="6" t="s">
@@ -15096,6 +15099,12 @@
       <c r="K101" s="60">
         <v>0.8</v>
       </c>
+      <c r="Q101" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R101" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="72">
@@ -15317,7 +15326,7 @@
         <v>239</v>
       </c>
       <c r="N109" s="55" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110">
@@ -15352,7 +15361,7 @@
         <v>239</v>
       </c>
       <c r="N110" s="55" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111">
@@ -15798,9 +15807,7 @@
       </c>
       <c r="F127" s="32"/>
       <c r="G127" s="32"/>
-      <c r="H127" s="6" t="s">
-        <v>238</v>
-      </c>
+      <c r="H127" s="6"/>
       <c r="I127" s="60" t="s">
         <v>112</v>
       </c>
@@ -15828,7 +15835,7 @@
         <v>55</v>
       </c>
       <c r="D128" s="6">
-        <v>0.0</v>
+        <v>1.5</v>
       </c>
       <c r="E128" s="6">
         <v>201042.0</v>

--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="263">
   <si>
     <t>To. 개발 : 스크립트 수정 시, 파란색으로 칠해둘 것!!</t>
   </si>
@@ -780,25 +780,25 @@
     <t>{fade a=3.5}사람들에게는 제 각기마다의 &lt;bounce a=0.2&gt;‘인연의 실’&lt;/bounce&gt;을 가지고 있단다. 사람들 간을 잇고 있는 실로, 그 사람의 인연을 나타내는 것이지.</t>
   </si>
   <si>
-    <t>{fade a=3.5}너에게는 끊겨져버린 &lt;color=#D80101&gt;홍연&lt;/&gt;과 어디로 이어진지 모른 채 길게 늘어진 &lt;color=#001AFF&gt;청연&lt;/&gt;이 보이는구나.</t>
+    <t>{fade a=3.5}너에게는 끊겨져버린 &lt;color=#D80101&gt;홍연&lt;/color&gt;과 어디로 이어진지 모른 채 길게 늘어진 &lt;color=#001AFF&gt;청연&lt;/color&gt;이 보이는구나.</t>
   </si>
   <si>
     <t>무엇을 물을까?</t>
   </si>
   <si>
-    <t>&lt;color=#D80101&gt;홍연이요?&lt;/&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#001AFF&gt;청연이요?&lt;/&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{fade a=3.5}&lt;color=#D80101&gt;붉은색 인연의 실&lt;/&gt;로, &lt;b&gt;연결된 자와 무조건 이어진다는 의미&lt;/b&gt;를 가지고 있지. </t>
+    <t>&lt;color=#D80101&gt;홍연&lt;/color&gt;이요?</t>
+  </si>
+  <si>
+    <t>&lt;color=#001AFF&gt;청연&lt;/color&gt;이요?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{fade a=3.5}&lt;color=#D80101&gt;붉은색 인연의 실&lt;/color&gt;로, &lt;b&gt;연결된 자와 무조건 이어진다는 의미&lt;/b&gt;를 가지고 있지. </t>
   </si>
   <si>
     <t>{fade a=3.5}끊겨져 있는 걸 보아하니, 어쩌면 네가 이 곳에 떨어진 것과 조금 연관이 있어 보이는구나.</t>
   </si>
   <si>
-    <t xml:space="preserve">{fade a=3.5}&lt;color=#001AFF&gt;푸른색 인연의 실&lt;/&gt;로, &lt;b&gt;연결된 자와는 끝내 이어지지 않는다는 의미&lt;/b&gt;를 가지고 있지. </t>
+    <t xml:space="preserve">{fade a=3.5}&lt;color=#001AFF&gt;푸른색 인연의 실&lt;/color&gt;로, &lt;b&gt;연결된 자와는 끝내 이어지지 않는다는 의미&lt;/b&gt;를 가지고 있지. </t>
   </si>
   <si>
     <t>{fade a=3.5}너에게 연결된 청연의 끝이 안 보이는 걸 보아하니, 어쩌면 그 답을 이 구천에서 찾을 수 있지 않을까 싶구나.</t>
@@ -837,7 +837,7 @@
     <t>{fade a=3.5}나에게는 너를 도울 힘이 남아있지 않지만, 너에게는 아직 너를 도울 힘이 남아있단다.</t>
   </si>
   <si>
-    <t>{fade a=3.5}&lt;b&gt;너의 인연의 실들.&lt;/b&gt; &lt;color=#D80101&gt;홍연&lt;/&gt;과 &lt;color=#001AFF&gt;청연.&lt;/&gt; 그것들이 너를 도와줄 것이야.</t>
+    <t>{fade a=3.5}&lt;b&gt;너의 인연의 실들.&lt;/b&gt; &lt;color=#D80101&gt;홍연&lt;/color&gt;과 &lt;color=#001AFF&gt;청연.&lt;/color&gt; 그것들이 너를 도와줄 것이야.</t>
   </si>
   <si>
     <t>{fade a=3.5}제 인연의 실들이요?</t>
@@ -880,6 +880,12 @@
   </si>
   <si>
     <t>{fade a=3.5}그렇지 웅단아?</t>
+  </si>
+  <si>
+    <t>카메라 페이드 아웃</t>
+  </si>
+  <si>
+    <t>FadeOut</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1412,7 @@
     <xdr:ext cx="3524250" cy="695325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1434,7 +1440,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1462,7 +1468,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image2.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -4465,8 +4471,8 @@
         <v>Bubble</v>
       </c>
       <c r="C128" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="D128" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
@@ -4479,19 +4485,31 @@
         <v>201042</v>
       </c>
       <c r="B129" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
-        <v>End</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Camera")</f>
+        <v>Camera</v>
       </c>
       <c r="C129" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D129" s="34"/>
+      <c r="D129" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201043.0)</f>
+        <v>201043</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="34"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="34"/>
+      <c r="A130" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201043.0)</f>
+        <v>201043</v>
+      </c>
+      <c r="B130" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"End")</f>
+        <v>End</v>
+      </c>
+      <c r="C130" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="D130" s="34"/>
     </row>
     <row r="131">
@@ -9815,6 +9833,12 @@
       <c r="B1017" s="34"/>
       <c r="C1017" s="34"/>
       <c r="D1017" s="34"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="34"/>
+      <c r="B1018" s="34"/>
+      <c r="C1018" s="34"/>
+      <c r="D1018" s="34"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10276,8 +10300,8 @@
         <v>Yeonong_Idle</v>
       </c>
       <c r="D27" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}너에게는 끊겨져버린 &lt;color=#D80101&gt;홍연&lt;/&gt;과 어디로 이어진지 모른 채 길게 늘어진 &lt;color=#001AFF&gt;청연&lt;/&gt;이 보이는구나.")</f>
-        <v>{fade a=3.5}너에게는 끊겨져버린 &lt;color=#D80101&gt;홍연&lt;/&gt;과 어디로 이어진지 모른 채 길게 늘어진 &lt;color=#001AFF&gt;청연&lt;/&gt;이 보이는구나.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}너에게는 끊겨져버린 &lt;color=#D80101&gt;홍연&lt;/color&gt;과 어디로 이어진지 모른 채 길게 늘어진 &lt;color=#001AFF&gt;청연&lt;/color&gt;이 보이는구나.")</f>
+        <v>{fade a=3.5}너에게는 끊겨져버린 &lt;color=#D80101&gt;홍연&lt;/color&gt;과 어디로 이어진지 모른 채 길게 늘어진 &lt;color=#001AFF&gt;청연&lt;/color&gt;이 보이는구나.</v>
       </c>
     </row>
     <row r="28">
@@ -10288,8 +10312,8 @@
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
       <c r="D28" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"&lt;color=#D80101&gt;홍연이요?&lt;/&gt;")</f>
-        <v>&lt;color=#D80101&gt;홍연이요?&lt;/&gt;</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"&lt;color=#D80101&gt;홍연&lt;/color&gt;이요?")</f>
+        <v>&lt;color=#D80101&gt;홍연&lt;/color&gt;이요?</v>
       </c>
     </row>
     <row r="29">
@@ -10300,8 +10324,8 @@
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
       <c r="D29" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"&lt;color=#001AFF&gt;청연이요?&lt;/&gt;")</f>
-        <v>&lt;color=#001AFF&gt;청연이요?&lt;/&gt;</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"&lt;color=#001AFF&gt;청연&lt;/color&gt;이요?")</f>
+        <v>&lt;color=#001AFF&gt;청연&lt;/color&gt;이요?</v>
       </c>
     </row>
     <row r="30">
@@ -10318,8 +10342,8 @@
         <v>Yeonong_Idle</v>
       </c>
       <c r="D30" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}&lt;color=#D80101&gt;붉은색 인연의 실&lt;/&gt;로, &lt;b&gt;연결된 자와 무조건 이어진다는 의미&lt;/b&gt;를 가지고 있지. ")</f>
-        <v>{fade a=3.5}&lt;color=#D80101&gt;붉은색 인연의 실&lt;/&gt;로, &lt;b&gt;연결된 자와 무조건 이어진다는 의미&lt;/b&gt;를 가지고 있지. </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}&lt;color=#D80101&gt;붉은색 인연의 실&lt;/color&gt;로, &lt;b&gt;연결된 자와 무조건 이어진다는 의미&lt;/b&gt;를 가지고 있지. ")</f>
+        <v>{fade a=3.5}&lt;color=#D80101&gt;붉은색 인연의 실&lt;/color&gt;로, &lt;b&gt;연결된 자와 무조건 이어진다는 의미&lt;/b&gt;를 가지고 있지. </v>
       </c>
     </row>
     <row r="31">
@@ -10354,8 +10378,8 @@
         <v>Yeonong_Idle</v>
       </c>
       <c r="D32" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}&lt;color=#001AFF&gt;푸른색 인연의 실&lt;/&gt;로, &lt;b&gt;연결된 자와는 끝내 이어지지 않는다는 의미&lt;/b&gt;를 가지고 있지. ")</f>
-        <v>{fade a=3.5}&lt;color=#001AFF&gt;푸른색 인연의 실&lt;/&gt;로, &lt;b&gt;연결된 자와는 끝내 이어지지 않는다는 의미&lt;/b&gt;를 가지고 있지. </v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}&lt;color=#001AFF&gt;푸른색 인연의 실&lt;/color&gt;로, &lt;b&gt;연결된 자와는 끝내 이어지지 않는다는 의미&lt;/b&gt;를 가지고 있지. ")</f>
+        <v>{fade a=3.5}&lt;color=#001AFF&gt;푸른색 인연의 실&lt;/color&gt;로, &lt;b&gt;연결된 자와는 끝내 이어지지 않는다는 의미&lt;/b&gt;를 가지고 있지. </v>
       </c>
     </row>
     <row r="33">
@@ -10534,8 +10558,8 @@
         <v>Yeonong_Idle</v>
       </c>
       <c r="D42" s="34" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}&lt;b&gt;너의 인연의 실들.&lt;/b&gt; &lt;color=#D80101&gt;홍연&lt;/&gt;과 &lt;color=#001AFF&gt;청연.&lt;/&gt; 그것들이 너를 도와줄 것이야.")</f>
-        <v>{fade a=3.5}&lt;b&gt;너의 인연의 실들.&lt;/b&gt; &lt;color=#D80101&gt;홍연&lt;/&gt;과 &lt;color=#001AFF&gt;청연.&lt;/&gt; 그것들이 너를 도와줄 것이야.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"{fade a=3.5}&lt;b&gt;너의 인연의 실들.&lt;/b&gt; &lt;color=#D80101&gt;홍연&lt;/color&gt;과 &lt;color=#001AFF&gt;청연.&lt;/color&gt; 그것들이 너를 도와줄 것이야.")</f>
+        <v>{fade a=3.5}&lt;b&gt;너의 인연의 실들.&lt;/b&gt; &lt;color=#D80101&gt;홍연&lt;/color&gt;과 &lt;color=#001AFF&gt;청연.&lt;/color&gt; 그것들이 너를 도와줄 것이야.</v>
       </c>
     </row>
     <row r="43">
@@ -11377,6 +11401,22 @@
       <c r="E38" s="34">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),201042.0)</f>
+        <v>201042</v>
+      </c>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FadeOut")</f>
+        <v>FadeOut</v>
+      </c>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -15835,7 +15875,7 @@
         <v>55</v>
       </c>
       <c r="D128" s="6">
-        <v>1.5</v>
+        <v>0.0</v>
       </c>
       <c r="E128" s="6">
         <v>201042.0</v>
@@ -15843,8 +15883,6 @@
       <c r="F128" s="32"/>
       <c r="G128" s="32"/>
       <c r="H128" s="32"/>
-      <c r="I128" s="32"/>
-      <c r="J128" s="32"/>
       <c r="O128" s="6" t="s">
         <v>238</v>
       </c>
@@ -15853,33 +15891,45 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="6">
+      <c r="A129" s="4">
         <v>201042.0</v>
       </c>
-      <c r="B129" s="81" t="s">
+      <c r="B129" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D129" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E129" s="4">
+        <v>201043.0</v>
+      </c>
+      <c r="I129" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="J129" s="32"/>
+      <c r="K129" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6">
+        <v>201043.0</v>
+      </c>
+      <c r="B130" s="78" t="s">
         <v>207</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C130" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D130" s="6">
         <v>0.0</v>
       </c>
-      <c r="E129" s="6" t="s">
+      <c r="E130" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F129" s="32"/>
-      <c r="G129" s="32"/>
-      <c r="H129" s="32"/>
-      <c r="I129" s="32"/>
-      <c r="J129" s="32"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="32"/>
-      <c r="B130" s="81"/>
-      <c r="C130" s="32"/>
-      <c r="D130" s="32"/>
-      <c r="E130" s="32"/>
       <c r="F130" s="32"/>
       <c r="G130" s="32"/>
       <c r="H130" s="32"/>
@@ -15887,8 +15937,8 @@
       <c r="J130" s="32"/>
     </row>
     <row r="131">
-      <c r="A131" s="32"/>
-      <c r="B131" s="32"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="81"/>
       <c r="C131" s="32"/>
       <c r="D131" s="32"/>
       <c r="E131" s="32"/>
@@ -15994,6 +16044,18 @@
       <c r="I139" s="32"/>
       <c r="J139" s="32"/>
     </row>
+    <row r="140">
+      <c r="A140" s="32"/>
+      <c r="B140" s="32"/>
+      <c r="C140" s="32"/>
+      <c r="D140" s="32"/>
+      <c r="E140" s="32"/>
+      <c r="F140" s="32"/>
+      <c r="G140" s="32"/>
+      <c r="H140" s="32"/>
+      <c r="I140" s="32"/>
+      <c r="J140" s="32"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/03. Data/DialogueData.xlsx
@@ -1412,7 +1412,7 @@
     <xdr:ext cx="3524250" cy="695325"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1440,7 +1440,7 @@
     <xdr:ext cx="1847850" cy="838200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="이미지"/>
+        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -11310,8 +11310,8 @@
         <v>0.05</v>
       </c>
       <c r="E33" s="34">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -14939,7 +14939,7 @@
         <v>0.05</v>
       </c>
       <c r="K94" s="6">
-        <v>0.8</v>
+        <v>0.0</v>
       </c>
       <c r="O94" s="4" t="s">
         <v>21</v>
